--- a/Final_Figures_and_Sheets_Singleset/pc_subset_statistics.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/pc_subset_statistics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2151,12 +2151,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2173,28 +2173,28 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>2.421027674426409e-08</v>
+        <v>3.359567535096329e-05</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>2.421027674426409e-08</v>
+        <v>3.359567535096329e-05</v>
       </c>
       <c r="I44" t="n">
-        <v>2.421027674426409e-08</v>
+        <v>3.359567535096329e-05</v>
       </c>
       <c r="J44" t="n">
-        <v>2.421027674426409e-08</v>
+        <v>3.359567535096329e-05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2204,35 +2204,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C57BL6 SLO</t>
+          <t>BALBc SLO</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>3.804200731235569e-08</v>
+        <v>1.546352435270545e-05</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>3.804200731235569e-08</v>
+        <v>1.546352435270545e-05</v>
       </c>
       <c r="I45" t="n">
-        <v>3.804200731235569e-08</v>
+        <v>1.546352435270545e-05</v>
       </c>
       <c r="J45" t="n">
-        <v>3.804200731235569e-08</v>
+        <v>1.546352435270545e-05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2249,30 +2249,30 @@
         <v>351</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0001793036813244824</v>
+        <v>0.003841069892775649</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0010454018419825</v>
+        <v>0.0124584707824063</v>
       </c>
       <c r="H46" t="n">
-        <v>1e-10</v>
+        <v>0.0001560695445890689</v>
       </c>
       <c r="I46" t="n">
         <v>1e-10</v>
       </c>
       <c r="J46" t="n">
-        <v>0.01373626373626374</v>
+        <v>0.1298374481398354</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2282,37 +2282,37 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0002918303611938361</v>
+        <v>0.003137554897246738</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0006606674447046341</v>
+        <v>0.005895087738759004</v>
       </c>
       <c r="H47" t="n">
-        <v>1e-10</v>
+        <v>0.0005423588090110582</v>
       </c>
       <c r="I47" t="n">
         <v>1e-10</v>
       </c>
       <c r="J47" t="n">
-        <v>0.00209036674685734</v>
+        <v>0.02561993927125506</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2322,37 +2322,37 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F48" t="n">
-        <v>6.584785430660611e-05</v>
+        <v>0.02037857630641449</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0001725252261978092</v>
+        <v>0.03183341262958958</v>
       </c>
       <c r="H48" t="n">
-        <v>1e-10</v>
+        <v>0.003563120332911217</v>
       </c>
       <c r="I48" t="n">
         <v>1e-10</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0005973715651135006</v>
+        <v>0.1298374481398354</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2362,37 +2362,37 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0003413018274171861</v>
+        <v>0.003286253696933951</v>
       </c>
       <c r="G49" t="n">
-        <v>0.001613543227772865</v>
+        <v>0.006235928720882601</v>
       </c>
       <c r="H49" t="n">
-        <v>1e-10</v>
+        <v>0.0003766775959320904</v>
       </c>
       <c r="I49" t="n">
         <v>1e-10</v>
       </c>
       <c r="J49" t="n">
-        <v>0.01373626373626374</v>
+        <v>0.02511755485893417</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2402,37 +2402,37 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F50" t="n">
-        <v>0.01378739586109934</v>
+        <v>0.1239965672663515</v>
       </c>
       <c r="G50" t="n">
-        <v>0.01409274180296961</v>
+        <v>0.06055778486462893</v>
       </c>
       <c r="H50" t="n">
-        <v>0.009044002761324164</v>
+        <v>0.1377995642701525</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0008048289738430583</v>
+        <v>0.0264367816091954</v>
       </c>
       <c r="J50" t="n">
-        <v>0.03666062547748293</v>
+        <v>0.2303149606299213</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2442,37 +2442,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0653784493116835</v>
+        <v>0.1135201107547094</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1117229507973507</v>
+        <v>0.07291384672095469</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02480726872743406</v>
+        <v>0.09392655367231638</v>
       </c>
       <c r="I51" t="n">
-        <v>0.002699055330634278</v>
+        <v>0.03000652315720809</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2912121375763823</v>
+        <v>0.2654973091488937</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2482,37 +2482,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F52" t="n">
-        <v>0.09569225485783588</v>
+        <v>0.1908883625322063</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1712020415227733</v>
+        <v>0.1199418988754651</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0346335656213705</v>
+        <v>0.1953842119066352</v>
       </c>
       <c r="I52" t="n">
-        <v>0.001819723721307796</v>
+        <v>0.06048387096774194</v>
       </c>
       <c r="J52" t="n">
-        <v>0.6783511846802986</v>
+        <v>0.3883058470764618</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2522,37 +2522,37 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0007295757529845903</v>
+        <v>0.006022360126647493</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0009159181551378159</v>
+        <v>0.007332903936349811</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0002660406885758999</v>
+        <v>0.003676383277734006</v>
       </c>
       <c r="I53" t="n">
-        <v>2.106361671058048e-05</v>
+        <v>1e-10</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00209036674685734</v>
+        <v>0.02561993927125506</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2562,37 +2562,37 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0001646194857665153</v>
+        <v>0.03862976429704315</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0002526463930603215</v>
+        <v>0.03711625316260054</v>
       </c>
       <c r="H54" t="n">
-        <v>1.914549458536297e-05</v>
+        <v>0.02254583830547549</v>
       </c>
       <c r="I54" t="n">
-        <v>1e-10</v>
+        <v>0.001016498553444366</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0005973715651135006</v>
+        <v>0.1298374481398354</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2602,37 +2602,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0007023437586346392</v>
+        <v>0.005909382049512451</v>
       </c>
       <c r="G55" t="n">
-        <v>0.002270856540591734</v>
+        <v>0.007895919537348587</v>
       </c>
       <c r="H55" t="n">
-        <v>3.417167851284855e-05</v>
+        <v>0.001495784266602579</v>
       </c>
       <c r="I55" t="n">
         <v>1e-10</v>
       </c>
       <c r="J55" t="n">
-        <v>0.01373626373626374</v>
+        <v>0.02511755485893417</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2646,33 +2646,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0001608007619559388</v>
+        <v>0.006619255615802541</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0003888368842493282</v>
+        <v>0.01787674881724896</v>
       </c>
       <c r="H56" t="n">
-        <v>1e-10</v>
+        <v>0.0004516031913292187</v>
       </c>
       <c r="I56" t="n">
         <v>1e-10</v>
       </c>
       <c r="J56" t="n">
-        <v>0.001748251748251748</v>
+        <v>0.1298374481398354</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2682,37 +2682,37 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>C57BL6</t>
+          <t>BALBc</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0004981482768320325</v>
+        <v>0.006573421445716165</v>
       </c>
       <c r="G57" t="n">
-        <v>0.001850667606973988</v>
+        <v>0.008194600073936747</v>
       </c>
       <c r="H57" t="n">
-        <v>3.142223311526303e-05</v>
+        <v>0.003899286987522281</v>
       </c>
       <c r="I57" t="n">
         <v>1e-10</v>
       </c>
       <c r="J57" t="n">
-        <v>0.01373626373626374</v>
+        <v>0.03733737301728747</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2729,28 +2729,28 @@
         <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0001720323163889472</v>
+        <v>9.542409372055383e-06</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>0.0001720323163889472</v>
+        <v>9.542409372055383e-06</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0001720323163889472</v>
+        <v>9.542409372055383e-06</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0001720323163889472</v>
+        <v>9.542409372055383e-06</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2760,35 +2760,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>C57BL6 SLO</t>
+          <t>BALBc SLO</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>8.775872385622115e-05</v>
+        <v>7.038161880903741e-06</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>8.775872385622115e-05</v>
+        <v>7.038161880903741e-06</v>
       </c>
       <c r="I59" t="n">
-        <v>8.775872385622115e-05</v>
+        <v>7.038161880903741e-06</v>
       </c>
       <c r="J59" t="n">
-        <v>8.775872385622115e-05</v>
+        <v>7.038161880903741e-06</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2805,30 +2805,30 @@
         <v>351</v>
       </c>
       <c r="F60" t="n">
-        <v>0.001357784249957524</v>
+        <v>0.005335151404721343</v>
       </c>
       <c r="G60" t="n">
-        <v>0.006784993900018669</v>
+        <v>0.02449839158359827</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0001018507740658829</v>
+        <v>0.0002297794117647059</v>
       </c>
       <c r="I60" t="n">
         <v>1e-10</v>
       </c>
       <c r="J60" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.3612068965517241</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2838,37 +2838,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0009386401959776724</v>
+        <v>0.01568832854923998</v>
       </c>
       <c r="G61" t="n">
-        <v>0.001987478386181893</v>
+        <v>0.04104372569023736</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0001358634119831529</v>
+        <v>0.005559126778931315</v>
       </c>
       <c r="I61" t="n">
         <v>1e-10</v>
       </c>
       <c r="J61" t="n">
-        <v>0.007447192936082791</v>
+        <v>0.2432895488292404</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2878,37 +2878,37 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0002915015961118109</v>
+        <v>0.007372248433427151</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0004936605498207121</v>
+        <v>0.009886743056055696</v>
       </c>
       <c r="H62" t="n">
-        <v>8.549906820507024e-05</v>
+        <v>0.004145541907734258</v>
       </c>
       <c r="I62" t="n">
         <v>1e-10</v>
       </c>
       <c r="J62" t="n">
-        <v>0.001654259718775848</v>
+        <v>0.0419550028415739</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2918,37 +2918,37 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="F63" t="n">
-        <v>0.002929806070046308</v>
+        <v>0.01454722153457655</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01158820516102467</v>
+        <v>0.05995496607321834</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0002349394052117391</v>
+        <v>0.0006272819472616634</v>
       </c>
       <c r="I63" t="n">
         <v>1e-10</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.3612068965517241</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2958,37 +2958,37 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>0.01873325133359</v>
+        <v>0.1533053740486822</v>
       </c>
       <c r="G64" t="n">
-        <v>0.01815902970821065</v>
+        <v>0.1185444919006652</v>
       </c>
       <c r="H64" t="n">
-        <v>0.01269850865824583</v>
+        <v>0.1158402203856749</v>
       </c>
       <c r="I64" t="n">
-        <v>0.002012072434607646</v>
+        <v>0.04300766283524905</v>
       </c>
       <c r="J64" t="n">
-        <v>0.04134812873811623</v>
+        <v>0.4321200621010868</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2998,37 +2998,37 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F65" t="n">
-        <v>0.07242901958775724</v>
+        <v>0.09618431378982538</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1216934767535491</v>
+        <v>0.04146843965394423</v>
       </c>
       <c r="H65" t="n">
-        <v>0.02762087044684924</v>
+        <v>0.09206818822203437</v>
       </c>
       <c r="I65" t="n">
-        <v>0.002699055330634278</v>
+        <v>0.01686702078091511</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3177961069057589</v>
+        <v>0.1566008903062919</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3038,37 +3038,37 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1177067489647653</v>
+        <v>0.2125566417460026</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1986969152852034</v>
+        <v>0.1131917509001985</v>
       </c>
       <c r="H66" t="n">
-        <v>0.04236875725900116</v>
+        <v>0.2356821589205397</v>
       </c>
       <c r="I66" t="n">
-        <v>0.002251004204466345</v>
+        <v>0.08585858585858586</v>
       </c>
       <c r="J66" t="n">
-        <v>0.7838364167478091</v>
+        <v>0.4089955022488755</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3078,37 +3078,37 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F67" t="n">
-        <v>0.002206263735744019</v>
+        <v>0.01137906045225346</v>
       </c>
       <c r="G67" t="n">
-        <v>0.002799790483118688</v>
+        <v>0.01665868759875335</v>
       </c>
       <c r="H67" t="n">
-        <v>0.001339833875045143</v>
+        <v>0.005516010649440897</v>
       </c>
       <c r="I67" t="n">
-        <v>0.00010990619808392</v>
+        <v>0.0001277465508431272</v>
       </c>
       <c r="J67" t="n">
-        <v>0.007447192936082791</v>
+        <v>0.06744025735294118</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3118,37 +3118,37 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0006358154308081924</v>
+        <v>0.01372332189776431</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0006588645032822923</v>
+        <v>0.01058544098746387</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0004333618544944671</v>
+        <v>0.01060787364809551</v>
       </c>
       <c r="I68" t="n">
-        <v>1e-10</v>
+        <v>0.00285973355653205</v>
       </c>
       <c r="J68" t="n">
-        <v>0.001654259718775848</v>
+        <v>0.0419550028415739</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3158,37 +3158,37 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="F69" t="n">
-        <v>0.00586441549288639</v>
+        <v>0.02835853481854809</v>
       </c>
       <c r="G69" t="n">
-        <v>0.01619140864001013</v>
+        <v>0.08362307315959486</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0008121813370499013</v>
+        <v>0.003676591072950121</v>
       </c>
       <c r="I69" t="n">
         <v>1e-10</v>
       </c>
       <c r="J69" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.3612068965517241</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3202,33 +3202,33 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0008885225506659297</v>
+        <v>0.006242101374407694</v>
       </c>
       <c r="G70" t="n">
-        <v>0.003057935996836243</v>
+        <v>0.03028536673807029</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0002406016065531423</v>
+        <v>0.0002436647173489279</v>
       </c>
       <c r="I70" t="n">
         <v>1e-10</v>
       </c>
       <c r="J70" t="n">
-        <v>0.02465483234714004</v>
+        <v>0.3612068965517241</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3238,37 +3238,37 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>C57BL6</t>
+          <t>BALBc</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="F71" t="n">
-        <v>0.003827417221277741</v>
+        <v>0.01050577554256063</v>
       </c>
       <c r="G71" t="n">
-        <v>0.01183024932797594</v>
+        <v>0.0143738679007556</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0005860944663521397</v>
+        <v>0.003990017037214345</v>
       </c>
       <c r="I71" t="n">
         <v>1e-10</v>
       </c>
       <c r="J71" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.06297438330170778</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3285,28 +3285,28 @@
         <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>1.701669145658016e-05</v>
+        <v>1.8798567824958e-08</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>1.701669145658016e-05</v>
+        <v>1.8798567824958e-08</v>
       </c>
       <c r="I72" t="n">
-        <v>1.701669145658016e-05</v>
+        <v>1.8798567824958e-08</v>
       </c>
       <c r="J72" t="n">
-        <v>1.701669145658016e-05</v>
+        <v>1.8798567824958e-08</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3316,35 +3316,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>C57BL6 SLO</t>
+          <t>BALBc SLO</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>1.467332858777236e-05</v>
+        <v>1.770839963494805e-08</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>1.467332858777236e-05</v>
+        <v>1.770839963494805e-08</v>
       </c>
       <c r="I73" t="n">
-        <v>1.467332858777236e-05</v>
+        <v>1.770839963494805e-08</v>
       </c>
       <c r="J73" t="n">
-        <v>1.467332858777236e-05</v>
+        <v>1.770839963494805e-08</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3361,30 +3361,30 @@
         <v>351</v>
       </c>
       <c r="F74" t="n">
-        <v>0.00156318209524434</v>
+        <v>0.0008175587393700756</v>
       </c>
       <c r="G74" t="n">
-        <v>0.006004885923264748</v>
+        <v>0.00313049436571063</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0001166393293238564</v>
+        <v>1e-10</v>
       </c>
       <c r="I74" t="n">
         <v>1e-10</v>
       </c>
       <c r="J74" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.02492163009404389</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3394,37 +3394,37 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0006819178293232456</v>
+        <v>0.000787200918875655</v>
       </c>
       <c r="G75" t="n">
-        <v>0.001503025368410236</v>
+        <v>0.001850426172576335</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0001709401709401709</v>
+        <v>1e-10</v>
       </c>
       <c r="I75" t="n">
         <v>1e-10</v>
       </c>
       <c r="J75" t="n">
-        <v>0.005866243295602451</v>
+        <v>0.008042279411764705</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3434,37 +3434,37 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0004735873163531046</v>
+        <v>0.002166012508279952</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0005693307558712308</v>
+        <v>0.00386240947918552</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0002648893113267449</v>
+        <v>1e-10</v>
       </c>
       <c r="I76" t="n">
-        <v>1.404547926184987e-05</v>
+        <v>1e-10</v>
       </c>
       <c r="J76" t="n">
-        <v>0.001792114695340502</v>
+        <v>0.01678200113662956</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3474,37 +3474,37 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="F77" t="n">
-        <v>0.00413839432406681</v>
+        <v>0.001660845964871429</v>
       </c>
       <c r="G77" t="n">
-        <v>0.01032114186948946</v>
+        <v>0.005080068202927074</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0003167754444414102</v>
+        <v>1e-10</v>
       </c>
       <c r="I77" t="n">
         <v>1e-10</v>
       </c>
       <c r="J77" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.02492163009404389</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3514,37 +3514,37 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F78" t="n">
-        <v>0.01830293056415361</v>
+        <v>0.1110869758627698</v>
       </c>
       <c r="G78" t="n">
-        <v>0.01841813831561883</v>
+        <v>0.06005988057694094</v>
       </c>
       <c r="H78" t="n">
-        <v>0.01249398426806507</v>
+        <v>0.1119834710743802</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0008048289738430583</v>
+        <v>0.02337164750957854</v>
       </c>
       <c r="J78" t="n">
-        <v>0.04611802715041417</v>
+        <v>0.218996062992126</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3554,37 +3554,37 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F79" t="n">
-        <v>0.07203826284162722</v>
+        <v>0.07177760607017061</v>
       </c>
       <c r="G79" t="n">
-        <v>0.121418083652622</v>
+        <v>0.04116030840136316</v>
       </c>
       <c r="H79" t="n">
-        <v>0.02669367846374238</v>
+        <v>0.05656522964215272</v>
       </c>
       <c r="I79" t="n">
-        <v>0.004048582995951417</v>
+        <v>0.01463050973814183</v>
       </c>
       <c r="J79" t="n">
-        <v>0.3174463121950434</v>
+        <v>0.142316125174407</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3594,37 +3594,37 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1207251175552363</v>
+        <v>0.1740538735091588</v>
       </c>
       <c r="G80" t="n">
-        <v>0.1798045491683578</v>
+        <v>0.1174125733497413</v>
       </c>
       <c r="H80" t="n">
-        <v>0.04912950058072009</v>
+        <v>0.1670600576973512</v>
       </c>
       <c r="I80" t="n">
-        <v>0.002392906887476745</v>
+        <v>0.05593607305936073</v>
       </c>
       <c r="J80" t="n">
-        <v>0.6994482310938007</v>
+        <v>0.3754122938530735</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3634,37 +3634,37 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F81" t="n">
-        <v>0.001475078536629758</v>
+        <v>0.00157440173775131</v>
       </c>
       <c r="G81" t="n">
-        <v>0.002222573773506424</v>
+        <v>0.002395265318140285</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0004371729850940279</v>
+        <v>0.0003874846241708035</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0001709401709401709</v>
+        <v>1e-10</v>
       </c>
       <c r="J81" t="n">
-        <v>0.005866243295602451</v>
+        <v>0.008042279411764705</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3674,37 +3674,37 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0008875956794729296</v>
+        <v>0.004332024916559905</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0007234781577193988</v>
+        <v>0.004558374925665803</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0008125975979961076</v>
+        <v>0.002940681839338276</v>
       </c>
       <c r="I82" t="n">
-        <v>7.530968347609874e-05</v>
+        <v>1e-10</v>
       </c>
       <c r="J82" t="n">
-        <v>0.001792114695340502</v>
+        <v>0.01678200113662956</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3714,37 +3714,37 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>0.005864110052350202</v>
+        <v>0.002987139420094652</v>
       </c>
       <c r="G83" t="n">
-        <v>0.01358509054079972</v>
+        <v>0.006904784781538031</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0004610280962762836</v>
+        <v>0.0002680789290362793</v>
       </c>
       <c r="I83" t="n">
         <v>1e-10</v>
       </c>
       <c r="J83" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.02492163009404389</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3758,62 +3758,3398 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="F84" t="n">
-        <v>0.002913788566514799</v>
+        <v>0.001176976386735722</v>
       </c>
       <c r="G84" t="n">
-        <v>0.009460211715598001</v>
+        <v>0.00375277121922223</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0001289617895205159</v>
+        <v>1e-10</v>
       </c>
       <c r="I84" t="n">
         <v>1e-10</v>
       </c>
       <c r="J84" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.02492163009404389</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>within strain across epitope</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>BALBc</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>36</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.002801771410407316</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.005339767173145868</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.0007512368721568554</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.02432721440028516</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoires</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>B10BR SLO</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2.421027674426409e-08</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="n">
+        <v>2.421027674426409e-08</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2.421027674426409e-08</v>
+      </c>
+      <c r="J86" t="n">
+        <v>2.421027674426409e-08</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoires</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>C57BL6 SLO</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>3.804200731235569e-08</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="n">
+        <v>3.804200731235569e-08</v>
+      </c>
+      <c r="I87" t="n">
+        <v>3.804200731235569e-08</v>
+      </c>
+      <c r="J87" t="n">
+        <v>3.804200731235569e-08</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>across strain across epitope</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>351</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.0001793036813244824</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.0010454018419825</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.01373626373626374</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>15</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.0002918303611938361</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.0006606674447046341</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.00209036674685734</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>15</v>
+      </c>
+      <c r="F90" t="n">
+        <v>6.584785430660611e-05</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.0001725252261978092</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.0005973715651135006</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>105</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.0003413018274171861</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.001613543227772865</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.01373626373626374</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.01378739586109934</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.01409274180296961</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.009044002761324164</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.0008048289738430583</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.03666062547748293</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.0653784493116835</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.1117229507973507</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.02480726872743406</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.002699055330634278</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.2912121375763823</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>15</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.09569225485783588</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.1712020415227733</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.0346335656213705</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.001819723721307796</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.6783511846802986</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.0007295757529845903</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.0009159181551378159</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.0002660406885758999</v>
+      </c>
+      <c r="I95" t="n">
+        <v>2.106361671058048e-05</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.00209036674685734</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.0001646194857665153</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.0002526463930603215</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1.914549458536297e-05</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.0005973715651135006</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>24</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.0009376235312714902</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.002894938962258286</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2.359485413862638e-05</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.01373626373626374</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>within strain across epitope</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>B10BR</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>66</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.0001608007619559388</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.0003888368842493282</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.001748251748251748</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CDR3</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>within strain across epitope</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>C57BL6</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>105</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.0004981482768320325</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.001850667606973988</v>
+      </c>
+      <c r="H99" t="n">
+        <v>3.142223311526303e-05</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.01373626373626374</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoires</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>B10BR SLO</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.0001720323163889472</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="n">
+        <v>0.0001720323163889472</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.0001720323163889472</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.0001720323163889472</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoires</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>C57BL6 SLO</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="n">
+        <v>8.775872385622115e-05</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>8.775872385622115e-05</v>
+      </c>
+      <c r="I101" t="n">
+        <v>8.775872385622115e-05</v>
+      </c>
+      <c r="J101" t="n">
+        <v>8.775872385622115e-05</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>across strain across epitope</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>351</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.001357784249957524</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.006784993900018669</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.0001018507740658829</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.1025641025641026</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>15</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.0009386401959776724</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.001987478386181893</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.0001358634119831529</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.007447192936082791</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>15</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.0002915015961118109</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.0004936605498207121</v>
+      </c>
+      <c r="H104" t="n">
+        <v>8.549906820507024e-05</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.001654259718775848</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>105</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.002929806070046308</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.01158820516102467</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.0002349394052117391</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.1025641025641026</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.01873325133359</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.01815902970821065</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.01269850865824583</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.002012072434607646</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.04134812873811623</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.07242901958775724</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.1216934767535491</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.02762087044684924</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.002699055330634278</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.3177961069057589</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>15</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.1177067489647653</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.1986969152852034</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.04236875725900116</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.002251004204466345</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.7838364167478091</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.002206263735744019</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.002799790483118688</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.001339833875045143</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.00010990619808392</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.007447192936082791</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.0006358154308081924</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.0006588645032822923</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.0004333618544944671</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.001654259718775848</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>24</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.009983094096589722</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.02268585527548247</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.001438198110649631</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.1025641025641026</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>within strain across epitope</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>B10BR</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>66</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.0008885225506659297</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.003057935996836243</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.0002406016065531423</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.02465483234714004</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CDR3a</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>within strain across epitope</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>C57BL6</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>105</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.003827417221277741</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.01183024932797594</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.0005860944663521397</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0.1025641025641026</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
           <t>CDR3b</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoires</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>B10BR SLO</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.701669145658016e-05</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="n">
+        <v>1.701669145658016e-05</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1.701669145658016e-05</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1.701669145658016e-05</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoires</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>C57BL6 SLO</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.467332858777236e-05</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="n">
+        <v>1.467332858777236e-05</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1.467332858777236e-05</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1.467332858777236e-05</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>across strain across epitope</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>351</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.00156318209524434</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.006004885923264748</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.0001166393293238564</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>15</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.0006819178293232456</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.001503025368410236</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.0001709401709401709</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.005866243295602451</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>15</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.0004735873163531046</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.0005693307558712308</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.0002648893113267449</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1.404547926184987e-05</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.001792114695340502</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>105</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.00413839432406681</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.01032114186948946</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.0003167754444414102</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.01830293056415361</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.01841813831561883</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.01249398426806507</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.0008048289738430583</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.04611802715041417</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.07203826284162722</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.121418083652622</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.02669367846374238</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.004048582995951417</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3174463121950434</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>15</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.1207251175552363</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.1798045491683578</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.04912950058072009</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.002392906887476745</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.6994482310938007</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.001475078536629758</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.002222573773506424</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.0004371729850940279</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.0001709401709401709</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.005866243295602451</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.0008875956794729296</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.0007234781577193988</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.0008125975979961076</v>
+      </c>
+      <c r="I124" t="n">
+        <v>7.530968347609874e-05</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.001792114695340502</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>24</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.0065734267501531</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.01744592197712574</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.0003672589470422005</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
         <is>
           <t>within strain across epitope</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>B10BR</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>66</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.002913788566514799</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.009460211715598001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.0001289617895205159</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CDR3b</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>within strain across epitope</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
         <is>
           <t>C57BL6</t>
         </is>
       </c>
-      <c r="E85" t="n">
+      <c r="E127" t="n">
         <v>105</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F127" t="n">
         <v>0.001970456538947975</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G127" t="n">
         <v>0.006787103068719874</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H127" t="n">
         <v>0.0002616615333156802</v>
       </c>
-      <c r="I85" t="n">
-        <v>1e-10</v>
-      </c>
-      <c r="J85" t="n">
+      <c r="I127" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J127" t="n">
         <v>0.05505354246627782</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoires</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>B10BR SLO</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3.359567535096329e-05</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="n">
+        <v>3.359567535096329e-05</v>
+      </c>
+      <c r="I128" t="n">
+        <v>3.359567535096329e-05</v>
+      </c>
+      <c r="J128" t="n">
+        <v>3.359567535096329e-05</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoires</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>C57BL6 SLO</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2.074796723341422e-05</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="n">
+        <v>2.074796723341422e-05</v>
+      </c>
+      <c r="I129" t="n">
+        <v>2.074796723341422e-05</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2.074796723341422e-05</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>across strain across epitope</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>351</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.0006132730888222901</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.004669820961287701</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.07869142351900972</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>15</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.0007107329337501481</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.001731023111951273</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I131" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.006585617206085569</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>15</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.0001813538622679531</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.0004380732483695505</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.001654259718775848</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>105</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.00119275371239902</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.007911281178785258</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.07869142351900972</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.01744451826846779</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.01747433436661695</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.01027528297205356</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.002012072434607646</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.03935650867508528</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.07142657893881711</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.1209568733332108</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.02642042788738032</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.002699055330634278</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.3154219881427934</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>15</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.1141523492731125</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.1987283490520821</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.04112311265969803</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.002023959911649705</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.7838364167478091</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.001776832184375371</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.002473236667838158</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.0008884073672806067</v>
+      </c>
+      <c r="I137" t="n">
+        <v>8.529722014482592e-05</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.006585617206085569</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.0004533845056698827</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.0006239723845847699</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.0002034902918496013</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.001654259718775848</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>24</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.004972107133601986</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.01623351868778429</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.0001526090710009458</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.07869142351900972</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>within strain across epitope</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>B10BR</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>66</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.0002522947927066079</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.0005222205163126044</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.002065727699530516</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>FullAlpha</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>within strain across epitope</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>C57BL6</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>105</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.00187572583855634</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.008419683839266418</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.0001368724205373087</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.07869142351900972</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoires</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>B10BR SLO</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" t="n">
+        <v>9.542409372055383e-06</v>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="n">
+        <v>9.542409372055383e-06</v>
+      </c>
+      <c r="I142" t="n">
+        <v>9.542409372055383e-06</v>
+      </c>
+      <c r="J142" t="n">
+        <v>9.542409372055383e-06</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoires</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>C57BL6 SLO</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" t="n">
+        <v>4.229840548900228e-06</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="n">
+        <v>4.229840548900228e-06</v>
+      </c>
+      <c r="I143" t="n">
+        <v>4.229840548900228e-06</v>
+      </c>
+      <c r="J143" t="n">
+        <v>4.229840548900228e-06</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>across strain across epitope</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>351</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.0006672593507086774</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.004079177228659587</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>15</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.0005846332388229272</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.00150859366225173</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.005801834236175474</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>15</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.0002646067452343278</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.000501578880896486</v>
+      </c>
+      <c r="H146" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0.001792114695340502</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>105</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.001545263980266946</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.007167011087992708</v>
+      </c>
+      <c r="H147" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>6</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.01825061588086396</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.01837529630922191</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.01242408352711722</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.0008048289738430583</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0.04603169399517733</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>6</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.0707023386035134</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.1193737107616653</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.02665003718277858</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.002699055330634278</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0.3119050196698437</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>15</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.1206402025239933</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.1798477052462389</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.04909088269454123</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.002351826384723962</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0.6994482310938007</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>6</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.001461582947057318</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.002198706884570174</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.0004317061800069566</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0.0001709401709401709</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0.005801834236175474</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>6</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.0006615167130858196</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.0006239814110789641</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.0005608903234266378</v>
+      </c>
+      <c r="I152" t="n">
+        <v>5.678889812611355e-05</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0.001792114695340502</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>24</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.004197648683610351</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.01411356377273175</v>
+      </c>
+      <c r="H153" t="n">
+        <v>7.086736649094887e-05</v>
+      </c>
+      <c r="I153" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>within strain across epitope</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>B10BR</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>66</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.001489590561339832</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.008416703420893446</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I154" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>within strain across epitope</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>C57BL6</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>105</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.0007271833896643908</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.002377425261538886</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.0001086748339176088</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0.01774267399267399</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoires</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>B10BR SLO</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1.8798567824958e-08</v>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="n">
+        <v>1.8798567824958e-08</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1.8798567824958e-08</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1.8798567824958e-08</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoires</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>C57BL6 SLO</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" t="n">
+        <v>3.361573602129544e-08</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="n">
+        <v>3.361573602129544e-08</v>
+      </c>
+      <c r="I157" t="n">
+        <v>3.361573602129544e-08</v>
+      </c>
+      <c r="J157" t="n">
+        <v>3.361573602129544e-08</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>across strain across epitope</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>351</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.0001223230370342846</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.0008839366484923771</v>
+      </c>
+      <c r="H158" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I158" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0.01316391941391941</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>15</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.000262027803149796</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.0006490796332874673</v>
+      </c>
+      <c r="H159" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0.002010064542896434</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>15</v>
+      </c>
+      <c r="F160" t="n">
+        <v>9.716814164090766e-06</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2.926066774436934e-05</v>
+      </c>
+      <c r="H160" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I160" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0.000112051646723871</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>within epitope across strain</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>105</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.0002112219088001026</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.001309629263361664</v>
+      </c>
+      <c r="H161" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I161" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0.01316391941391941</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>6</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.0132924043330923</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.01378842037119685</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.008130115296339259</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.0008048289738430583</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0.03568908297225431</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>6</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.06491605844543795</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.1114547575746722</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.02431553598418002</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.002699055330634278</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0.2902769796241488</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>within epitope within mice</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>15</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.09496163749346424</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.1713332084655425</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.03448577235772358</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.001781364639873021</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0.6783511846802986</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>6</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.00065506935787449</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.0009331071264840125</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.0001056162745872558</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0.002010064542896434</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>6</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2.429188541022691e-05</v>
+      </c>
+      <c r="G166" t="n">
+        <v>4.441235516734016e-05</v>
+      </c>
+      <c r="H166" t="n">
+        <v>2.514461256123818e-06</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0.000112051646723871</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>within strain &amp; epitope across mice</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>24</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.0007199912139491496</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.00268952024789428</v>
+      </c>
+      <c r="H167" t="n">
+        <v>8.551598018112292e-08</v>
+      </c>
+      <c r="I167" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0.01316391941391941</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>within strain across epitope</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>B10BR</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>66</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.0001285736718507947</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.0003778472440203651</v>
+      </c>
+      <c r="H168" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I168" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0.001748251748251748</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>within strain across epitope</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>C57BL6</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>105</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.0003280905300655374</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.001572139698737131</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1.60296883767597e-05</v>
+      </c>
+      <c r="I169" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0.01316391941391941</v>
       </c>
     </row>
   </sheetData>

--- a/Final_Figures_and_Sheets_Singleset/pc_subset_statistics.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/pc_subset_statistics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J169"/>
+  <dimension ref="A1:J193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,29 +493,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B10BR SLO</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>351</v>
       </c>
       <c r="F2" t="n">
-        <v>2.421027674426409e-08</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>0.001180690302270171</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.004029079249844817</v>
+      </c>
       <c r="H2" t="n">
-        <v>2.421027674426409e-08</v>
+        <v>1e-10</v>
       </c>
       <c r="I2" t="n">
-        <v>2.421027674426409e-08</v>
+        <v>1e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>2.421027674426409e-08</v>
+        <v>0.03254132231404959</v>
       </c>
     </row>
     <row r="3">
@@ -531,29 +533,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BALBc SLO</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.949841837061067e-08</v>
+        <v>1e-10</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>1.949841837061067e-08</v>
+        <v>1e-10</v>
       </c>
       <c r="I3" t="n">
-        <v>1.949841837061067e-08</v>
+        <v>1e-10</v>
       </c>
       <c r="J3" t="n">
-        <v>1.949841837061067e-08</v>
+        <v>1e-10</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +571,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>351</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001180690302270171</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.004029079249844817</v>
-      </c>
+        <v>2.421027674426409e-08</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1e-10</v>
+        <v>2.421027674426409e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1e-10</v>
+        <v>2.421027674426409e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03254132231404959</v>
+        <v>2.421027674426409e-08</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>B10BR SLO × BALBc SLO</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002020998152574061</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.005778179792142927</v>
-      </c>
+        <v>8.7710385535849e-10</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>1e-10</v>
+        <v>8.7710385535849e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>1e-10</v>
+        <v>8.7710385535849e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03254132231404959</v>
+        <v>8.7710385535849e-10</v>
       </c>
     </row>
     <row r="6">
@@ -649,31 +647,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>BALBc SLO</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003881599054915728</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.006216601710609679</v>
-      </c>
+        <v>1.949841837061067e-08</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.0002789984457592244</v>
+        <v>1.949841837061067e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1e-10</v>
+        <v>1.949841837061067e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02969348659003831</v>
+        <v>1.949841837061067e-08</v>
       </c>
     </row>
     <row r="7">
@@ -689,22 +685,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001708162759223309</v>
+        <v>0.002020998152574061</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005090660286303507</v>
+        <v>0.005778179792142927</v>
       </c>
       <c r="H7" t="n">
         <v>1e-10</v>
@@ -713,7 +709,7 @@
         <v>1e-10</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02492163009404389</v>
+        <v>0.03254132231404959</v>
       </c>
     </row>
     <row r="8">
@@ -729,31 +725,31 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1130139883081409</v>
+        <v>0.003881599054915728</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06190296085141628</v>
+        <v>0.006216601710609679</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1119834710743802</v>
+        <v>0.0002789984457592244</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02423371647509578</v>
+        <v>1e-10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2241633858267716</v>
+        <v>0.02969348659003831</v>
       </c>
     </row>
     <row r="9">
@@ -769,31 +765,31 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07417495418824581</v>
+        <v>0.001708162759223309</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04043240977290872</v>
+        <v>0.005090660286303507</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05677655677655678</v>
+        <v>1e-10</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01463050973814183</v>
+        <v>1e-10</v>
       </c>
       <c r="J9" t="n">
-        <v>0.142316125174407</v>
+        <v>0.02492163009404389</v>
       </c>
     </row>
     <row r="10">
@@ -809,31 +805,31 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>B10BR</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>153</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1829993087415615</v>
+        <v>0.001917638767158118</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1187468112845635</v>
+        <v>0.005247453474697337</v>
       </c>
       <c r="H10" t="n">
-        <v>0.196422428620571</v>
+        <v>3.892868265337901e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05846774193548387</v>
+        <v>1e-10</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3862068965517241</v>
+        <v>0.03254132231404959</v>
       </c>
     </row>
     <row r="11">
@@ -849,31 +845,31 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>BALBc</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>0.004041996205148123</v>
+        <v>0.003194489031888061</v>
       </c>
       <c r="G11" t="n">
-        <v>0.007751728715109926</v>
+        <v>0.00540934987451879</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0009208705732769904</v>
+        <v>0.001381154342614789</v>
       </c>
       <c r="I11" t="n">
         <v>1e-10</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03254132231404959</v>
+        <v>0.02437176973801461</v>
       </c>
     </row>
     <row r="12">
@@ -889,31 +885,31 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>18</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007763198009831456</v>
+        <v>0.004041996205148123</v>
       </c>
       <c r="G12" t="n">
-        <v>0.006903577984969865</v>
+        <v>0.007751728715109926</v>
       </c>
       <c r="H12" t="n">
-        <v>0.005659722496133016</v>
+        <v>0.0009208705732769904</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0005579967915184488</v>
+        <v>1e-10</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02969348659003831</v>
+        <v>0.03254132231404959</v>
       </c>
     </row>
     <row r="13">
@@ -929,31 +925,31 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>18</v>
       </c>
       <c r="F13" t="n">
-        <v>0.003081773008798411</v>
+        <v>0.007763198009831456</v>
       </c>
       <c r="G13" t="n">
-        <v>0.006901254756812606</v>
+        <v>0.006903577984969865</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0004493352135374697</v>
+        <v>0.005659722496133016</v>
       </c>
       <c r="I13" t="n">
-        <v>1e-10</v>
+        <v>0.0005579967915184488</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02492163009404389</v>
+        <v>0.02969348659003831</v>
       </c>
     </row>
     <row r="14">
@@ -969,31 +965,31 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B10BR</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001917638767158118</v>
+        <v>0.003081773008798411</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005247453474697337</v>
+        <v>0.006901254756812606</v>
       </c>
       <c r="H14" t="n">
-        <v>3.892868265337901e-05</v>
+        <v>0.0004493352135374697</v>
       </c>
       <c r="I14" t="n">
         <v>1e-10</v>
       </c>
       <c r="J14" t="n">
-        <v>0.03254132231404959</v>
+        <v>0.02492163009404389</v>
       </c>
     </row>
     <row r="15">
@@ -1009,31 +1005,31 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BALBc</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>0.003194489031888061</v>
+        <v>0.1130139883081409</v>
       </c>
       <c r="G15" t="n">
-        <v>0.00540934987451879</v>
+        <v>0.06190296085141628</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001381154342614789</v>
+        <v>0.1119834710743802</v>
       </c>
       <c r="I15" t="n">
-        <v>1e-10</v>
+        <v>0.02423371647509578</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02437176973801461</v>
+        <v>0.2241633858267716</v>
       </c>
     </row>
     <row r="16">
@@ -1044,34 +1040,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B10BR SLO</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001720323163889472</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
+        <v>0.07417495418824581</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.04043240977290872</v>
+      </c>
       <c r="H16" t="n">
-        <v>0.0001720323163889472</v>
+        <v>0.05677655677655678</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0001720323163889472</v>
+        <v>0.01463050973814183</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001720323163889472</v>
+        <v>0.142316125174407</v>
       </c>
     </row>
     <row r="17">
@@ -1082,34 +1080,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BALBc SLO</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>6.190664724656162e-05</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+        <v>0.1829993087415615</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.1187468112845635</v>
+      </c>
       <c r="H17" t="n">
-        <v>6.190664724656162e-05</v>
+        <v>0.196422428620571</v>
       </c>
       <c r="I17" t="n">
-        <v>6.190664724656162e-05</v>
+        <v>0.05846774193548387</v>
       </c>
       <c r="J17" t="n">
-        <v>6.190664724656162e-05</v>
+        <v>0.3862068965517241</v>
       </c>
     </row>
     <row r="18">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1165,31 +1165,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.004880275854174541</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.008406832704060917</v>
-      </c>
+        <v>7.68672735770055e-05</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.001364716864670765</v>
+        <v>7.68672735770055e-05</v>
       </c>
       <c r="I19" t="n">
-        <v>1e-10</v>
+        <v>7.68672735770055e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03389721074380166</v>
+        <v>7.68672735770055e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1205,31 +1203,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03654153393660983</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.04949247537992789</v>
-      </c>
+        <v>0.0001720323163889472</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.011828307272276</v>
+        <v>0.0001720323163889472</v>
       </c>
       <c r="I20" t="n">
-        <v>1e-10</v>
+        <v>0.0001720323163889472</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1730523627075351</v>
+        <v>0.0001720323163889472</v>
       </c>
     </row>
     <row r="21">
@@ -1245,31 +1241,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>B10BR SLO × BALBc SLO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.006304085795593883</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.01564305615222577</v>
-      </c>
+        <v>6.609534173726737e-05</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.0009355072035899857</v>
+        <v>6.609534173726737e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>1e-10</v>
+        <v>6.609534173726737e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.08967741935483871</v>
+        <v>6.609534173726737e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1285,31 +1279,29 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>BALBc SLO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1271358008998325</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.06217867109138069</v>
-      </c>
+        <v>6.190664724656162e-05</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1377995642701525</v>
+        <v>6.190664724656162e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02998084291187739</v>
+        <v>6.190664724656162e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2358513779527559</v>
+        <v>6.190664724656162e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1325,31 +1317,31 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1307033759604007</v>
+        <v>0.004880275854174541</v>
       </c>
       <c r="G23" t="n">
-        <v>0.07746428858048253</v>
+        <v>0.008406832704060917</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1304592843054382</v>
+        <v>0.001364716864670765</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03009971111732364</v>
+        <v>1e-10</v>
       </c>
       <c r="J23" t="n">
-        <v>0.265563749916949</v>
+        <v>0.03389721074380166</v>
       </c>
     </row>
     <row r="24">
@@ -1365,31 +1357,31 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2027239940962324</v>
+        <v>0.03654153393660983</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1234016843825638</v>
+        <v>0.04949247537992789</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2442278860569715</v>
+        <v>0.011828307272276</v>
       </c>
       <c r="I24" t="n">
-        <v>0.06048387096774194</v>
+        <v>1e-10</v>
       </c>
       <c r="J24" t="n">
-        <v>0.399400299850075</v>
+        <v>0.1730523627075351</v>
       </c>
     </row>
     <row r="25">
@@ -1405,31 +1397,31 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
-        <v>0.009188078470753279</v>
+        <v>0.006304085795593883</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01028131577687032</v>
+        <v>0.01564305615222577</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00618445984730186</v>
+        <v>0.0009355072035899857</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0003386222910216718</v>
+        <v>1e-10</v>
       </c>
       <c r="J25" t="n">
-        <v>0.03389721074380166</v>
+        <v>0.08967741935483871</v>
       </c>
     </row>
     <row r="26">
@@ -1445,28 +1437,28 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>B10BR</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>18</v>
+        <v>153</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06830056854722485</v>
+        <v>0.0112287473712485</v>
       </c>
       <c r="G26" t="n">
-        <v>0.05372098166782383</v>
+        <v>0.0284197280151805</v>
       </c>
       <c r="H26" t="n">
-        <v>0.04637231648725901</v>
+        <v>0.0008081896551724138</v>
       </c>
       <c r="I26" t="n">
-        <v>0.008084172895677607</v>
+        <v>1e-10</v>
       </c>
       <c r="J26" t="n">
         <v>0.1730523627075351</v>
@@ -1485,25 +1477,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>BALBc</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01172917130044606</v>
+        <v>0.010954056793088</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0209136546879961</v>
+        <v>0.01668035084879519</v>
       </c>
       <c r="H27" t="n">
-        <v>0.003701283745894416</v>
+        <v>0.006414544707609642</v>
       </c>
       <c r="I27" t="n">
         <v>1e-10</v>
@@ -1525,31 +1517,31 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B10BR</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0112287473712485</v>
+        <v>0.009188078470753279</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0284197280151805</v>
+        <v>0.01028131577687032</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0008081896551724138</v>
+        <v>0.00618445984730186</v>
       </c>
       <c r="I28" t="n">
-        <v>1e-10</v>
+        <v>0.0003386222910216718</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1730523627075351</v>
+        <v>0.03389721074380166</v>
       </c>
     </row>
     <row r="29">
@@ -1565,31 +1557,31 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BALBc</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
-        <v>0.010954056793088</v>
+        <v>0.06830056854722485</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01668035084879519</v>
+        <v>0.05372098166782383</v>
       </c>
       <c r="H29" t="n">
-        <v>0.006414544707609642</v>
+        <v>0.04637231648725901</v>
       </c>
       <c r="I29" t="n">
-        <v>1e-10</v>
+        <v>0.008084172895677607</v>
       </c>
       <c r="J29" t="n">
-        <v>0.08967741935483871</v>
+        <v>0.1730523627075351</v>
       </c>
     </row>
     <row r="30">
@@ -1600,34 +1592,36 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B10BR SLO</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F30" t="n">
-        <v>1.701669145658016e-05</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
+        <v>0.01172917130044606</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0209136546879961</v>
+      </c>
       <c r="H30" t="n">
-        <v>1.701669145658016e-05</v>
+        <v>0.003701283745894416</v>
       </c>
       <c r="I30" t="n">
-        <v>1.701669145658016e-05</v>
+        <v>1e-10</v>
       </c>
       <c r="J30" t="n">
-        <v>1.701669145658016e-05</v>
+        <v>0.08967741935483871</v>
       </c>
     </row>
     <row r="31">
@@ -1638,34 +1632,36 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BALBc SLO</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F31" t="n">
-        <v>1.314238148647551e-05</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
+        <v>0.1271358008998325</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.06217867109138069</v>
+      </c>
       <c r="H31" t="n">
-        <v>1.314238148647551e-05</v>
+        <v>0.1377995642701525</v>
       </c>
       <c r="I31" t="n">
-        <v>1.314238148647551e-05</v>
+        <v>0.02998084291187739</v>
       </c>
       <c r="J31" t="n">
-        <v>1.314238148647551e-05</v>
+        <v>0.2358513779527559</v>
       </c>
     </row>
     <row r="32">
@@ -1676,36 +1672,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>351</v>
+        <v>9</v>
       </c>
       <c r="F32" t="n">
-        <v>0.005554557161335637</v>
+        <v>0.1307033759604007</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02456813708168561</v>
+        <v>0.07746428858048253</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0002658631690889755</v>
+        <v>0.1304592843054382</v>
       </c>
       <c r="I32" t="n">
-        <v>1e-10</v>
+        <v>0.03009971111732364</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3612068965517241</v>
+        <v>0.265563749916949</v>
       </c>
     </row>
     <row r="33">
@@ -1716,36 +1712,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0159873396196832</v>
+        <v>0.2027239940962324</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04101894209540102</v>
+        <v>0.1234016843825638</v>
       </c>
       <c r="H33" t="n">
-        <v>0.005629828136397379</v>
+        <v>0.2442278860569715</v>
       </c>
       <c r="I33" t="n">
-        <v>1e-10</v>
+        <v>0.06048387096774194</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2432895488292404</v>
+        <v>0.399400299850075</v>
       </c>
     </row>
     <row r="34">
@@ -1761,31 +1757,31 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>36</v>
+        <v>351</v>
       </c>
       <c r="F34" t="n">
-        <v>0.007546819954679976</v>
+        <v>0.005554557161335637</v>
       </c>
       <c r="G34" t="n">
-        <v>0.009925145672938144</v>
+        <v>0.02456813708168561</v>
       </c>
       <c r="H34" t="n">
-        <v>0.004145541907734258</v>
+        <v>0.0002658631690889755</v>
       </c>
       <c r="I34" t="n">
         <v>1e-10</v>
       </c>
       <c r="J34" t="n">
-        <v>0.04212215424731722</v>
+        <v>0.3612068965517241</v>
       </c>
     </row>
     <row r="35">
@@ -1801,31 +1797,29 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01454961617059187</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.05995464286652648</v>
-      </c>
+        <v>3.547367311941806e-05</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0.0006272819472616634</v>
+        <v>3.547367311941806e-05</v>
       </c>
       <c r="I35" t="n">
-        <v>1e-10</v>
+        <v>3.547367311941806e-05</v>
       </c>
       <c r="J35" t="n">
-        <v>0.3612068965517241</v>
+        <v>3.547367311941806e-05</v>
       </c>
     </row>
     <row r="36">
@@ -1841,31 +1835,29 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1535799255954132</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.118312441036203</v>
-      </c>
+        <v>1.701669145658016e-05</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0.1158402203856749</v>
+        <v>1.701669145658016e-05</v>
       </c>
       <c r="I36" t="n">
-        <v>0.04473180076628352</v>
+        <v>1.701669145658016e-05</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4321200621010868</v>
+        <v>1.701669145658016e-05</v>
       </c>
     </row>
     <row r="37">
@@ -1881,31 +1873,29 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>B10BR SLO × BALBc SLO</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.09687436840118567</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.04142393568009053</v>
-      </c>
+        <v>1.066659492406927e-05</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0.09707328872047086</v>
+        <v>1.066659492406927e-05</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01696020874103066</v>
+        <v>1.066659492406927e-05</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1567337718424025</v>
+        <v>1.066659492406927e-05</v>
       </c>
     </row>
     <row r="38">
@@ -1921,31 +1911,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>BALBc SLO</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2126239818133427</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.1131071023803552</v>
-      </c>
+        <v>1.314238148647551e-05</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0.2356821589205397</v>
+        <v>1.314238148647551e-05</v>
       </c>
       <c r="I38" t="n">
-        <v>0.08646464646464647</v>
+        <v>1.314238148647551e-05</v>
       </c>
       <c r="J38" t="n">
-        <v>0.4089955022488755</v>
+        <v>1.314238148647551e-05</v>
       </c>
     </row>
     <row r="39">
@@ -1961,7 +1949,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1970,22 +1958,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01165176648142849</v>
+        <v>0.0159873396196832</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01667216580845127</v>
+        <v>0.04101894209540102</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00558671200690696</v>
+        <v>0.005629828136397379</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0001277465508431272</v>
+        <v>1e-10</v>
       </c>
       <c r="J39" t="n">
-        <v>0.06744025735294118</v>
+        <v>0.2432895488292404</v>
       </c>
     </row>
     <row r="40">
@@ -2001,7 +1989,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2010,19 +1998,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01396118684971882</v>
+        <v>0.007546819954679976</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01058187415537509</v>
+        <v>0.009925145672938144</v>
       </c>
       <c r="H40" t="n">
-        <v>0.01140281509851912</v>
+        <v>0.004145541907734258</v>
       </c>
       <c r="I40" t="n">
-        <v>0.00285973355653205</v>
+        <v>1e-10</v>
       </c>
       <c r="J40" t="n">
         <v>0.04212215424731722</v>
@@ -2041,7 +2029,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2050,16 +2038,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F41" t="n">
-        <v>0.02835853481854809</v>
+        <v>0.01454961617059187</v>
       </c>
       <c r="G41" t="n">
-        <v>0.08362307315959486</v>
+        <v>0.05995464286652648</v>
       </c>
       <c r="H41" t="n">
-        <v>0.003676591072950121</v>
+        <v>0.0006272819472616634</v>
       </c>
       <c r="I41" t="n">
         <v>1e-10</v>
@@ -2081,7 +2069,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2121,7 +2109,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2156,34 +2144,36 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B10BR SLO</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F44" t="n">
-        <v>3.359567535096329e-05</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
+        <v>0.01165176648142849</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.01667216580845127</v>
+      </c>
       <c r="H44" t="n">
-        <v>3.359567535096329e-05</v>
+        <v>0.00558671200690696</v>
       </c>
       <c r="I44" t="n">
-        <v>3.359567535096329e-05</v>
+        <v>0.0001277465508431272</v>
       </c>
       <c r="J44" t="n">
-        <v>3.359567535096329e-05</v>
+        <v>0.06744025735294118</v>
       </c>
     </row>
     <row r="45">
@@ -2194,34 +2184,36 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BALBc SLO</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F45" t="n">
-        <v>1.546352435270545e-05</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
+        <v>0.01396118684971882</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.01058187415537509</v>
+      </c>
       <c r="H45" t="n">
-        <v>1.546352435270545e-05</v>
+        <v>0.01140281509851912</v>
       </c>
       <c r="I45" t="n">
-        <v>1.546352435270545e-05</v>
+        <v>0.00285973355653205</v>
       </c>
       <c r="J45" t="n">
-        <v>1.546352435270545e-05</v>
+        <v>0.04212215424731722</v>
       </c>
     </row>
     <row r="46">
@@ -2232,36 +2224,36 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>351</v>
+        <v>18</v>
       </c>
       <c r="F46" t="n">
-        <v>0.003841069892775649</v>
+        <v>0.02835853481854809</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0124584707824063</v>
+        <v>0.08362307315959486</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0001560695445890689</v>
+        <v>0.003676591072950121</v>
       </c>
       <c r="I46" t="n">
         <v>1e-10</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1298374481398354</v>
+        <v>0.3612068965517241</v>
       </c>
     </row>
     <row r="47">
@@ -2272,12 +2264,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2286,22 +2278,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>0.003137554897246738</v>
+        <v>0.1535799255954132</v>
       </c>
       <c r="G47" t="n">
-        <v>0.005895087738759004</v>
+        <v>0.118312441036203</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0005423588090110582</v>
+        <v>0.1158402203856749</v>
       </c>
       <c r="I47" t="n">
-        <v>1e-10</v>
+        <v>0.04473180076628352</v>
       </c>
       <c r="J47" t="n">
-        <v>0.02561993927125506</v>
+        <v>0.4321200621010868</v>
       </c>
     </row>
     <row r="48">
@@ -2312,12 +2304,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2326,22 +2318,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F48" t="n">
-        <v>0.02037857630641449</v>
+        <v>0.09687436840118567</v>
       </c>
       <c r="G48" t="n">
-        <v>0.03183341262958958</v>
+        <v>0.04142393568009053</v>
       </c>
       <c r="H48" t="n">
-        <v>0.003563120332911217</v>
+        <v>0.09707328872047086</v>
       </c>
       <c r="I48" t="n">
-        <v>1e-10</v>
+        <v>0.01696020874103066</v>
       </c>
       <c r="J48" t="n">
-        <v>0.1298374481398354</v>
+        <v>0.1567337718424025</v>
       </c>
     </row>
     <row r="49">
@@ -2352,12 +2344,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2366,22 +2358,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
-        <v>0.003286253696933951</v>
+        <v>0.2126239818133427</v>
       </c>
       <c r="G49" t="n">
-        <v>0.006235928720882601</v>
+        <v>0.1131071023803552</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0003766775959320904</v>
+        <v>0.2356821589205397</v>
       </c>
       <c r="I49" t="n">
-        <v>1e-10</v>
+        <v>0.08646464646464647</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02511755485893417</v>
+        <v>0.4089955022488755</v>
       </c>
     </row>
     <row r="50">
@@ -2397,31 +2389,31 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>9</v>
+        <v>351</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1239965672663515</v>
+        <v>0.003841069892775649</v>
       </c>
       <c r="G50" t="n">
-        <v>0.06055778486462893</v>
+        <v>0.0124584707824063</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1377995642701525</v>
+        <v>0.0001560695445890689</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0264367816091954</v>
+        <v>1e-10</v>
       </c>
       <c r="J50" t="n">
-        <v>0.2303149606299213</v>
+        <v>0.1298374481398354</v>
       </c>
     </row>
     <row r="51">
@@ -2437,31 +2429,29 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1135201107547094</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.07291384672095469</v>
-      </c>
+        <v>1.83563638392849e-07</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>0.09392655367231638</v>
+        <v>1.83563638392849e-07</v>
       </c>
       <c r="I51" t="n">
-        <v>0.03000652315720809</v>
+        <v>1.83563638392849e-07</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2654973091488937</v>
+        <v>1.83563638392849e-07</v>
       </c>
     </row>
     <row r="52">
@@ -2477,31 +2467,29 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1908883625322063</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.1199418988754651</v>
-      </c>
+        <v>3.359567535096329e-05</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>0.1953842119066352</v>
+        <v>3.359567535096329e-05</v>
       </c>
       <c r="I52" t="n">
-        <v>0.06048387096774194</v>
+        <v>3.359567535096329e-05</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3883058470764618</v>
+        <v>3.359567535096329e-05</v>
       </c>
     </row>
     <row r="53">
@@ -2517,31 +2505,29 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>B10BR SLO × BALBc SLO</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>0.006022360126647493</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.007332903936349811</v>
-      </c>
+        <v>7.793067754860183e-07</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>0.003676383277734006</v>
+        <v>7.793067754860183e-07</v>
       </c>
       <c r="I53" t="n">
-        <v>1e-10</v>
+        <v>7.793067754860183e-07</v>
       </c>
       <c r="J53" t="n">
-        <v>0.02561993927125506</v>
+        <v>7.793067754860183e-07</v>
       </c>
     </row>
     <row r="54">
@@ -2557,31 +2543,29 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>BALBc SLO</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>0.03862976429704315</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.03711625316260054</v>
-      </c>
+        <v>1.546352435270545e-05</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>0.02254583830547549</v>
+        <v>1.546352435270545e-05</v>
       </c>
       <c r="I54" t="n">
-        <v>0.001016498553444366</v>
+        <v>1.546352435270545e-05</v>
       </c>
       <c r="J54" t="n">
-        <v>0.1298374481398354</v>
+        <v>1.546352435270545e-05</v>
       </c>
     </row>
     <row r="55">
@@ -2597,31 +2581,31 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F55" t="n">
-        <v>0.005909382049512451</v>
+        <v>0.003137554897246738</v>
       </c>
       <c r="G55" t="n">
-        <v>0.007895919537348587</v>
+        <v>0.005895087738759004</v>
       </c>
       <c r="H55" t="n">
-        <v>0.001495784266602579</v>
+        <v>0.0005423588090110582</v>
       </c>
       <c r="I55" t="n">
         <v>1e-10</v>
       </c>
       <c r="J55" t="n">
-        <v>0.02511755485893417</v>
+        <v>0.02561993927125506</v>
       </c>
     </row>
     <row r="56">
@@ -2637,25 +2621,25 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B10BR</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>153</v>
+        <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>0.006619255615802541</v>
+        <v>0.02037857630641449</v>
       </c>
       <c r="G56" t="n">
-        <v>0.01787674881724896</v>
+        <v>0.03183341262958958</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0004516031913292187</v>
+        <v>0.003563120332911217</v>
       </c>
       <c r="I56" t="n">
         <v>1e-10</v>
@@ -2677,31 +2661,31 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BALBc</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E57" t="n">
         <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>0.006573421445716165</v>
+        <v>0.003286253696933951</v>
       </c>
       <c r="G57" t="n">
-        <v>0.008194600073936747</v>
+        <v>0.006235928720882601</v>
       </c>
       <c r="H57" t="n">
-        <v>0.003899286987522281</v>
+        <v>0.0003766775959320904</v>
       </c>
       <c r="I57" t="n">
         <v>1e-10</v>
       </c>
       <c r="J57" t="n">
-        <v>0.03733737301728747</v>
+        <v>0.02511755485893417</v>
       </c>
     </row>
     <row r="58">
@@ -2712,34 +2696,36 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>B10BR SLO</t>
+          <t>B10BR</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="F58" t="n">
-        <v>9.542409372055383e-06</v>
-      </c>
-      <c r="G58" t="inlineStr"/>
+        <v>0.006619255615802541</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.01787674881724896</v>
+      </c>
       <c r="H58" t="n">
-        <v>9.542409372055383e-06</v>
+        <v>0.0004516031913292187</v>
       </c>
       <c r="I58" t="n">
-        <v>9.542409372055383e-06</v>
+        <v>1e-10</v>
       </c>
       <c r="J58" t="n">
-        <v>9.542409372055383e-06</v>
+        <v>0.1298374481398354</v>
       </c>
     </row>
     <row r="59">
@@ -2750,34 +2736,36 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BALBc SLO</t>
+          <t>BALBc</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>7.038161880903741e-06</v>
-      </c>
-      <c r="G59" t="inlineStr"/>
+        <v>0.006573421445716165</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.008194600073936747</v>
+      </c>
       <c r="H59" t="n">
-        <v>7.038161880903741e-06</v>
+        <v>0.003899286987522281</v>
       </c>
       <c r="I59" t="n">
-        <v>7.038161880903741e-06</v>
+        <v>1e-10</v>
       </c>
       <c r="J59" t="n">
-        <v>7.038161880903741e-06</v>
+        <v>0.03733737301728747</v>
       </c>
     </row>
     <row r="60">
@@ -2788,36 +2776,36 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>351</v>
+        <v>18</v>
       </c>
       <c r="F60" t="n">
-        <v>0.005335151404721343</v>
+        <v>0.006022360126647493</v>
       </c>
       <c r="G60" t="n">
-        <v>0.02449839158359827</v>
+        <v>0.007332903936349811</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0002297794117647059</v>
+        <v>0.003676383277734006</v>
       </c>
       <c r="I60" t="n">
         <v>1e-10</v>
       </c>
       <c r="J60" t="n">
-        <v>0.3612068965517241</v>
+        <v>0.02561993927125506</v>
       </c>
     </row>
     <row r="61">
@@ -2828,36 +2816,36 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F61" t="n">
-        <v>0.01568832854923998</v>
+        <v>0.03862976429704315</v>
       </c>
       <c r="G61" t="n">
-        <v>0.04104372569023736</v>
+        <v>0.03711625316260054</v>
       </c>
       <c r="H61" t="n">
-        <v>0.005559126778931315</v>
+        <v>0.02254583830547549</v>
       </c>
       <c r="I61" t="n">
-        <v>1e-10</v>
+        <v>0.001016498553444366</v>
       </c>
       <c r="J61" t="n">
-        <v>0.2432895488292404</v>
+        <v>0.1298374481398354</v>
       </c>
     </row>
     <row r="62">
@@ -2868,36 +2856,36 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F62" t="n">
-        <v>0.007372248433427151</v>
+        <v>0.005909382049512451</v>
       </c>
       <c r="G62" t="n">
-        <v>0.009886743056055696</v>
+        <v>0.007895919537348587</v>
       </c>
       <c r="H62" t="n">
-        <v>0.004145541907734258</v>
+        <v>0.001495784266602579</v>
       </c>
       <c r="I62" t="n">
         <v>1e-10</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0419550028415739</v>
+        <v>0.02511755485893417</v>
       </c>
     </row>
     <row r="63">
@@ -2908,36 +2896,36 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>0.01454722153457655</v>
+        <v>0.1239965672663515</v>
       </c>
       <c r="G63" t="n">
-        <v>0.05995496607321834</v>
+        <v>0.06055778486462893</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0006272819472616634</v>
+        <v>0.1377995642701525</v>
       </c>
       <c r="I63" t="n">
-        <v>1e-10</v>
+        <v>0.0264367816091954</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3612068965517241</v>
+        <v>0.2303149606299213</v>
       </c>
     </row>
     <row r="64">
@@ -2948,36 +2936,36 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1533053740486822</v>
+        <v>0.1135201107547094</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1185444919006652</v>
+        <v>0.07291384672095469</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1158402203856749</v>
+        <v>0.09392655367231638</v>
       </c>
       <c r="I64" t="n">
-        <v>0.04300766283524905</v>
+        <v>0.03000652315720809</v>
       </c>
       <c r="J64" t="n">
-        <v>0.4321200621010868</v>
+        <v>0.2654973091488937</v>
       </c>
     </row>
     <row r="65">
@@ -2988,36 +2976,36 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>9</v>
       </c>
       <c r="F65" t="n">
-        <v>0.09618431378982538</v>
+        <v>0.1908883625322063</v>
       </c>
       <c r="G65" t="n">
-        <v>0.04146843965394423</v>
+        <v>0.1199418988754651</v>
       </c>
       <c r="H65" t="n">
-        <v>0.09206818822203437</v>
+        <v>0.1953842119066352</v>
       </c>
       <c r="I65" t="n">
-        <v>0.01686702078091511</v>
+        <v>0.06048387096774194</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1566008903062919</v>
+        <v>0.3883058470764618</v>
       </c>
     </row>
     <row r="66">
@@ -3033,31 +3021,31 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>9</v>
+        <v>351</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2125566417460026</v>
+        <v>0.005335151404721343</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1131917509001985</v>
+        <v>0.02449839158359827</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2356821589205397</v>
+        <v>0.0002297794117647059</v>
       </c>
       <c r="I66" t="n">
-        <v>0.08585858585858586</v>
+        <v>1e-10</v>
       </c>
       <c r="J66" t="n">
-        <v>0.4089955022488755</v>
+        <v>0.3612068965517241</v>
       </c>
     </row>
     <row r="67">
@@ -3073,31 +3061,29 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>0.01137906045225346</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0.01665868759875335</v>
-      </c>
+        <v>1.376727287946367e-07</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>0.005516010649440897</v>
+        <v>1.376727287946367e-07</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0001277465508431272</v>
+        <v>1.376727287946367e-07</v>
       </c>
       <c r="J67" t="n">
-        <v>0.06744025735294118</v>
+        <v>1.376727287946367e-07</v>
       </c>
     </row>
     <row r="68">
@@ -3113,31 +3099,29 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0.01372332189776431</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0.01058544098746387</v>
-      </c>
+        <v>9.542409372055383e-06</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>0.01060787364809551</v>
+        <v>9.542409372055383e-06</v>
       </c>
       <c r="I68" t="n">
-        <v>0.00285973355653205</v>
+        <v>9.542409372055383e-06</v>
       </c>
       <c r="J68" t="n">
-        <v>0.0419550028415739</v>
+        <v>9.542409372055383e-06</v>
       </c>
     </row>
     <row r="69">
@@ -3153,31 +3137,29 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>B10BR SLO × BALBc SLO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0.02835853481854809</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0.08362307315959486</v>
-      </c>
+        <v>4.191510650939885e-06</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>0.003676591072950121</v>
+        <v>4.191510650939885e-06</v>
       </c>
       <c r="I69" t="n">
-        <v>1e-10</v>
+        <v>4.191510650939885e-06</v>
       </c>
       <c r="J69" t="n">
-        <v>0.3612068965517241</v>
+        <v>4.191510650939885e-06</v>
       </c>
     </row>
     <row r="70">
@@ -3193,31 +3175,29 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>B10BR</t>
+          <t>BALBc SLO</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0.006242101374407694</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0.03028536673807029</v>
-      </c>
+        <v>7.038161880903741e-06</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>0.0002436647173489279</v>
+        <v>7.038161880903741e-06</v>
       </c>
       <c r="I70" t="n">
-        <v>1e-10</v>
+        <v>7.038161880903741e-06</v>
       </c>
       <c r="J70" t="n">
-        <v>0.3612068965517241</v>
+        <v>7.038161880903741e-06</v>
       </c>
     </row>
     <row r="71">
@@ -3233,31 +3213,31 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BALBc</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>36</v>
       </c>
       <c r="F71" t="n">
-        <v>0.01050577554256063</v>
+        <v>0.01568832854923998</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0143738679007556</v>
+        <v>0.04104372569023736</v>
       </c>
       <c r="H71" t="n">
-        <v>0.003990017037214345</v>
+        <v>0.005559126778931315</v>
       </c>
       <c r="I71" t="n">
         <v>1e-10</v>
       </c>
       <c r="J71" t="n">
-        <v>0.06297438330170778</v>
+        <v>0.2432895488292404</v>
       </c>
     </row>
     <row r="72">
@@ -3268,34 +3248,36 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B10BR SLO</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F72" t="n">
-        <v>1.8798567824958e-08</v>
-      </c>
-      <c r="G72" t="inlineStr"/>
+        <v>0.007372248433427151</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.009886743056055696</v>
+      </c>
       <c r="H72" t="n">
-        <v>1.8798567824958e-08</v>
+        <v>0.004145541907734258</v>
       </c>
       <c r="I72" t="n">
-        <v>1.8798567824958e-08</v>
+        <v>1e-10</v>
       </c>
       <c r="J72" t="n">
-        <v>1.8798567824958e-08</v>
+        <v>0.0419550028415739</v>
       </c>
     </row>
     <row r="73">
@@ -3306,34 +3288,36 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BALBc SLO</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F73" t="n">
-        <v>1.770839963494805e-08</v>
-      </c>
-      <c r="G73" t="inlineStr"/>
+        <v>0.01454722153457655</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.05995496607321834</v>
+      </c>
       <c r="H73" t="n">
-        <v>1.770839963494805e-08</v>
+        <v>0.0006272819472616634</v>
       </c>
       <c r="I73" t="n">
-        <v>1.770839963494805e-08</v>
+        <v>1e-10</v>
       </c>
       <c r="J73" t="n">
-        <v>1.770839963494805e-08</v>
+        <v>0.3612068965517241</v>
       </c>
     </row>
     <row r="74">
@@ -3344,36 +3328,36 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>B10BR</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>351</v>
+        <v>153</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0008175587393700756</v>
+        <v>0.006242101374407694</v>
       </c>
       <c r="G74" t="n">
-        <v>0.00313049436571063</v>
+        <v>0.03028536673807029</v>
       </c>
       <c r="H74" t="n">
-        <v>1e-10</v>
+        <v>0.0002436647173489279</v>
       </c>
       <c r="I74" t="n">
         <v>1e-10</v>
       </c>
       <c r="J74" t="n">
-        <v>0.02492163009404389</v>
+        <v>0.3612068965517241</v>
       </c>
     </row>
     <row r="75">
@@ -3384,36 +3368,36 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>BALBc</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>36</v>
       </c>
       <c r="F75" t="n">
-        <v>0.000787200918875655</v>
+        <v>0.01050577554256063</v>
       </c>
       <c r="G75" t="n">
-        <v>0.001850426172576335</v>
+        <v>0.0143738679007556</v>
       </c>
       <c r="H75" t="n">
-        <v>1e-10</v>
+        <v>0.003990017037214345</v>
       </c>
       <c r="I75" t="n">
         <v>1e-10</v>
       </c>
       <c r="J75" t="n">
-        <v>0.008042279411764705</v>
+        <v>0.06297438330170778</v>
       </c>
     </row>
     <row r="76">
@@ -3424,36 +3408,36 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F76" t="n">
-        <v>0.002166012508279952</v>
+        <v>0.01137906045225346</v>
       </c>
       <c r="G76" t="n">
-        <v>0.00386240947918552</v>
+        <v>0.01665868759875335</v>
       </c>
       <c r="H76" t="n">
-        <v>1e-10</v>
+        <v>0.005516010649440897</v>
       </c>
       <c r="I76" t="n">
-        <v>1e-10</v>
+        <v>0.0001277465508431272</v>
       </c>
       <c r="J76" t="n">
-        <v>0.01678200113662956</v>
+        <v>0.06744025735294118</v>
       </c>
     </row>
     <row r="77">
@@ -3464,36 +3448,36 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F77" t="n">
-        <v>0.001660845964871429</v>
+        <v>0.01372332189776431</v>
       </c>
       <c r="G77" t="n">
-        <v>0.005080068202927074</v>
+        <v>0.01058544098746387</v>
       </c>
       <c r="H77" t="n">
-        <v>1e-10</v>
+        <v>0.01060787364809551</v>
       </c>
       <c r="I77" t="n">
-        <v>1e-10</v>
+        <v>0.00285973355653205</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02492163009404389</v>
+        <v>0.0419550028415739</v>
       </c>
     </row>
     <row r="78">
@@ -3504,36 +3488,36 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1110869758627698</v>
+        <v>0.02835853481854809</v>
       </c>
       <c r="G78" t="n">
-        <v>0.06005988057694094</v>
+        <v>0.08362307315959486</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1119834710743802</v>
+        <v>0.003676591072950121</v>
       </c>
       <c r="I78" t="n">
-        <v>0.02337164750957854</v>
+        <v>1e-10</v>
       </c>
       <c r="J78" t="n">
-        <v>0.218996062992126</v>
+        <v>0.3612068965517241</v>
       </c>
     </row>
     <row r="79">
@@ -3544,36 +3528,36 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E79" t="n">
         <v>9</v>
       </c>
       <c r="F79" t="n">
-        <v>0.07177760607017061</v>
+        <v>0.1533053740486822</v>
       </c>
       <c r="G79" t="n">
-        <v>0.04116030840136316</v>
+        <v>0.1185444919006652</v>
       </c>
       <c r="H79" t="n">
-        <v>0.05656522964215272</v>
+        <v>0.1158402203856749</v>
       </c>
       <c r="I79" t="n">
-        <v>0.01463050973814183</v>
+        <v>0.04300766283524905</v>
       </c>
       <c r="J79" t="n">
-        <v>0.142316125174407</v>
+        <v>0.4321200621010868</v>
       </c>
     </row>
     <row r="80">
@@ -3584,36 +3568,36 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E80" t="n">
         <v>9</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1740538735091588</v>
+        <v>0.09618431378982538</v>
       </c>
       <c r="G80" t="n">
-        <v>0.1174125733497413</v>
+        <v>0.04146843965394423</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1670600576973512</v>
+        <v>0.09206818822203437</v>
       </c>
       <c r="I80" t="n">
-        <v>0.05593607305936073</v>
+        <v>0.01686702078091511</v>
       </c>
       <c r="J80" t="n">
-        <v>0.3754122938530735</v>
+        <v>0.1566008903062919</v>
       </c>
     </row>
     <row r="81">
@@ -3624,36 +3608,36 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F81" t="n">
-        <v>0.00157440173775131</v>
+        <v>0.2125566417460026</v>
       </c>
       <c r="G81" t="n">
-        <v>0.002395265318140285</v>
+        <v>0.1131917509001985</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0003874846241708035</v>
+        <v>0.2356821589205397</v>
       </c>
       <c r="I81" t="n">
-        <v>1e-10</v>
+        <v>0.08585858585858586</v>
       </c>
       <c r="J81" t="n">
-        <v>0.008042279411764705</v>
+        <v>0.4089955022488755</v>
       </c>
     </row>
     <row r="82">
@@ -3669,31 +3653,31 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>351</v>
       </c>
       <c r="F82" t="n">
-        <v>0.004332024916559905</v>
+        <v>0.0008175587393700756</v>
       </c>
       <c r="G82" t="n">
-        <v>0.004558374925665803</v>
+        <v>0.00313049436571063</v>
       </c>
       <c r="H82" t="n">
-        <v>0.002940681839338276</v>
+        <v>1e-10</v>
       </c>
       <c r="I82" t="n">
         <v>1e-10</v>
       </c>
       <c r="J82" t="n">
-        <v>0.01678200113662956</v>
+        <v>0.02492163009404389</v>
       </c>
     </row>
     <row r="83">
@@ -3709,31 +3693,29 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VGP</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>0.002987139420094652</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0.006904784781538031</v>
-      </c>
+        <v>1e-10</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>0.0002680789290362793</v>
+        <v>1e-10</v>
       </c>
       <c r="I83" t="n">
         <v>1e-10</v>
       </c>
       <c r="J83" t="n">
-        <v>0.02492163009404389</v>
+        <v>1e-10</v>
       </c>
     </row>
     <row r="84">
@@ -3749,31 +3731,29 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>B10BR</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>0.001176976386735722</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0.00375277121922223</v>
-      </c>
+        <v>1.8798567824958e-08</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>1e-10</v>
+        <v>1.8798567824958e-08</v>
       </c>
       <c r="I84" t="n">
-        <v>1e-10</v>
+        <v>1.8798567824958e-08</v>
       </c>
       <c r="J84" t="n">
-        <v>0.02492163009404389</v>
+        <v>1.8798567824958e-08</v>
       </c>
     </row>
     <row r="85">
@@ -3789,138 +3769,138 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>BALBc</t>
+          <t>B10BR SLO × BALBc SLO</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>0.002801771410407316</v>
-      </c>
-      <c r="G85" t="n">
-        <v>0.005339767173145868</v>
-      </c>
+        <v>1.349390546705369e-10</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>0.0007512368721568554</v>
+        <v>1.349390546705369e-10</v>
       </c>
       <c r="I85" t="n">
-        <v>1e-10</v>
+        <v>1.349390546705369e-10</v>
       </c>
       <c r="J85" t="n">
-        <v>0.02432721440028516</v>
+        <v>1.349390546705369e-10</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>B10BR SLO</t>
+          <t>BALBc SLO</t>
         </is>
       </c>
       <c r="E86" t="n">
         <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>2.421027674426409e-08</v>
+        <v>1.770839963494805e-08</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>2.421027674426409e-08</v>
+        <v>1.770839963494805e-08</v>
       </c>
       <c r="I86" t="n">
-        <v>2.421027674426409e-08</v>
+        <v>1.770839963494805e-08</v>
       </c>
       <c r="J86" t="n">
-        <v>2.421027674426409e-08</v>
+        <v>1.770839963494805e-08</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>C57BL6 SLO</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F87" t="n">
-        <v>3.804200731235569e-08</v>
-      </c>
-      <c r="G87" t="inlineStr"/>
+        <v>0.000787200918875655</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.001850426172576335</v>
+      </c>
       <c r="H87" t="n">
-        <v>3.804200731235569e-08</v>
+        <v>1e-10</v>
       </c>
       <c r="I87" t="n">
-        <v>3.804200731235569e-08</v>
+        <v>1e-10</v>
       </c>
       <c r="J87" t="n">
-        <v>3.804200731235569e-08</v>
+        <v>0.008042279411764705</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>351</v>
+        <v>36</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0001793036813244824</v>
+        <v>0.002166012508279952</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0010454018419825</v>
+        <v>0.00386240947918552</v>
       </c>
       <c r="H88" t="n">
         <v>1e-10</v>
@@ -3929,38 +3909,38 @@
         <v>1e-10</v>
       </c>
       <c r="J88" t="n">
-        <v>0.01373626373626374</v>
+        <v>0.01678200113662956</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0002918303611938361</v>
+        <v>0.001660845964871429</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0006606674447046341</v>
+        <v>0.005080068202927074</v>
       </c>
       <c r="H89" t="n">
         <v>1e-10</v>
@@ -3969,38 +3949,38 @@
         <v>1e-10</v>
       </c>
       <c r="J89" t="n">
-        <v>0.00209036674685734</v>
+        <v>0.02492163009404389</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>B10BR</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F90" t="n">
-        <v>6.584785430660611e-05</v>
+        <v>0.001176976386735722</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0001725252261978092</v>
+        <v>0.00375277121922223</v>
       </c>
       <c r="H90" t="n">
         <v>1e-10</v>
@@ -4009,287 +3989,287 @@
         <v>1e-10</v>
       </c>
       <c r="J90" t="n">
-        <v>0.0005973715651135006</v>
+        <v>0.02492163009404389</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>BALBc</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0003413018274171861</v>
+        <v>0.002801771410407316</v>
       </c>
       <c r="G91" t="n">
-        <v>0.001613543227772865</v>
+        <v>0.005339767173145868</v>
       </c>
       <c r="H91" t="n">
-        <v>1e-10</v>
+        <v>0.0007512368721568554</v>
       </c>
       <c r="I91" t="n">
         <v>1e-10</v>
       </c>
       <c r="J91" t="n">
-        <v>0.01373626373626374</v>
+        <v>0.02432721440028516</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F92" t="n">
-        <v>0.01378739586109934</v>
+        <v>0.00157440173775131</v>
       </c>
       <c r="G92" t="n">
-        <v>0.01409274180296961</v>
+        <v>0.002395265318140285</v>
       </c>
       <c r="H92" t="n">
-        <v>0.009044002761324164</v>
+        <v>0.0003874846241708035</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0008048289738430583</v>
+        <v>1e-10</v>
       </c>
       <c r="J92" t="n">
-        <v>0.03666062547748293</v>
+        <v>0.008042279411764705</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0653784493116835</v>
+        <v>0.004332024916559905</v>
       </c>
       <c r="G93" t="n">
-        <v>0.1117229507973507</v>
+        <v>0.004558374925665803</v>
       </c>
       <c r="H93" t="n">
-        <v>0.02480726872743406</v>
+        <v>0.002940681839338276</v>
       </c>
       <c r="I93" t="n">
-        <v>0.002699055330634278</v>
+        <v>1e-10</v>
       </c>
       <c r="J93" t="n">
-        <v>0.2912121375763823</v>
+        <v>0.01678200113662956</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F94" t="n">
-        <v>0.09569225485783588</v>
+        <v>0.002987139420094652</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1712020415227733</v>
+        <v>0.006904784781538031</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0346335656213705</v>
+        <v>0.0002680789290362793</v>
       </c>
       <c r="I94" t="n">
-        <v>0.001819723721307796</v>
+        <v>1e-10</v>
       </c>
       <c r="J94" t="n">
-        <v>0.6783511846802986</v>
+        <v>0.02492163009404389</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0007295757529845903</v>
+        <v>0.1110869758627698</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0009159181551378159</v>
+        <v>0.06005988057694094</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0002660406885758999</v>
+        <v>0.1119834710743802</v>
       </c>
       <c r="I95" t="n">
-        <v>2.106361671058048e-05</v>
+        <v>0.02337164750957854</v>
       </c>
       <c r="J95" t="n">
-        <v>0.00209036674685734</v>
+        <v>0.218996062992126</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0001646194857665153</v>
+        <v>0.07177760607017061</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0002526463930603215</v>
+        <v>0.04116030840136316</v>
       </c>
       <c r="H96" t="n">
-        <v>1.914549458536297e-05</v>
+        <v>0.05656522964215272</v>
       </c>
       <c r="I96" t="n">
-        <v>1e-10</v>
+        <v>0.01463050973814183</v>
       </c>
       <c r="J96" t="n">
-        <v>0.0005973715651135006</v>
+        <v>0.142316125174407</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kd</t>
+          <t>Kb</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CDR3</t>
+          <t>FullChain</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>VGP</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0009376235312714902</v>
+        <v>0.1740538735091588</v>
       </c>
       <c r="G97" t="n">
-        <v>0.002894938962258286</v>
+        <v>0.1174125733497413</v>
       </c>
       <c r="H97" t="n">
-        <v>2.359485413862638e-05</v>
+        <v>0.1670600576973512</v>
       </c>
       <c r="I97" t="n">
-        <v>1e-10</v>
+        <v>0.05593607305936073</v>
       </c>
       <c r="J97" t="n">
-        <v>0.01373626373626374</v>
+        <v>0.3754122938530735</v>
       </c>
     </row>
     <row r="98">
@@ -4305,22 +4285,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>B10BR</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>66</v>
+        <v>351</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0001608007619559388</v>
+        <v>0.0001793036813244824</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0003888368842493282</v>
+        <v>0.0010454018419825</v>
       </c>
       <c r="H98" t="n">
         <v>1e-10</v>
@@ -4329,7 +4309,7 @@
         <v>1e-10</v>
       </c>
       <c r="J98" t="n">
-        <v>0.001748251748251748</v>
+        <v>0.01373626373626374</v>
       </c>
     </row>
     <row r="99">
@@ -4345,31 +4325,29 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>C57BL6</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0004981482768320325</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0.001850667606973988</v>
-      </c>
+        <v>1e-10</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>3.142223311526303e-05</v>
+        <v>1e-10</v>
       </c>
       <c r="I99" t="n">
         <v>1e-10</v>
       </c>
       <c r="J99" t="n">
-        <v>0.01373626373626374</v>
+        <v>1e-10</v>
       </c>
     </row>
     <row r="100">
@@ -4380,12 +4358,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4397,17 +4375,17 @@
         <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0001720323163889472</v>
+        <v>2.421027674426409e-08</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>0.0001720323163889472</v>
+        <v>2.421027674426409e-08</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0001720323163889472</v>
+        <v>2.421027674426409e-08</v>
       </c>
       <c r="J100" t="n">
-        <v>0.0001720323163889472</v>
+        <v>2.421027674426409e-08</v>
       </c>
     </row>
     <row r="101">
@@ -4418,34 +4396,34 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>C57BL6 SLO</t>
+          <t>B10BR SLO × C57BL6 SLO</t>
         </is>
       </c>
       <c r="E101" t="n">
         <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>8.775872385622115e-05</v>
+        <v>1.245975102399426e-09</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>8.775872385622115e-05</v>
+        <v>1.245975102399426e-09</v>
       </c>
       <c r="I101" t="n">
-        <v>8.775872385622115e-05</v>
+        <v>1.245975102399426e-09</v>
       </c>
       <c r="J101" t="n">
-        <v>8.775872385622115e-05</v>
+        <v>1.245975102399426e-09</v>
       </c>
     </row>
     <row r="102">
@@ -4456,36 +4434,34 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>C57BL6 SLO</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>351</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>0.001357784249957524</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0.006784993900018669</v>
-      </c>
+        <v>3.804200731235569e-08</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>0.0001018507740658829</v>
+        <v>3.804200731235569e-08</v>
       </c>
       <c r="I102" t="n">
-        <v>1e-10</v>
+        <v>3.804200731235569e-08</v>
       </c>
       <c r="J102" t="n">
-        <v>0.1025641025641026</v>
+        <v>3.804200731235569e-08</v>
       </c>
     </row>
     <row r="103">
@@ -4496,12 +4472,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4513,19 +4489,19 @@
         <v>15</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0009386401959776724</v>
+        <v>0.0002918303611938361</v>
       </c>
       <c r="G103" t="n">
-        <v>0.001987478386181893</v>
+        <v>0.0006606674447046341</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0001358634119831529</v>
+        <v>1e-10</v>
       </c>
       <c r="I103" t="n">
         <v>1e-10</v>
       </c>
       <c r="J103" t="n">
-        <v>0.007447192936082791</v>
+        <v>0.00209036674685734</v>
       </c>
     </row>
     <row r="104">
@@ -4536,12 +4512,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4553,19 +4529,19 @@
         <v>15</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0002915015961118109</v>
+        <v>6.584785430660611e-05</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0004936605498207121</v>
+        <v>0.0001725252261978092</v>
       </c>
       <c r="H104" t="n">
-        <v>8.549906820507024e-05</v>
+        <v>1e-10</v>
       </c>
       <c r="I104" t="n">
         <v>1e-10</v>
       </c>
       <c r="J104" t="n">
-        <v>0.001654259718775848</v>
+        <v>0.0005973715651135006</v>
       </c>
     </row>
     <row r="105">
@@ -4576,12 +4552,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4593,19 +4569,19 @@
         <v>105</v>
       </c>
       <c r="F105" t="n">
-        <v>0.002929806070046308</v>
+        <v>0.0003413018274171861</v>
       </c>
       <c r="G105" t="n">
-        <v>0.01158820516102467</v>
+        <v>0.001613543227772865</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0002349394052117391</v>
+        <v>1e-10</v>
       </c>
       <c r="I105" t="n">
         <v>1e-10</v>
       </c>
       <c r="J105" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.01373626373626374</v>
       </c>
     </row>
     <row r="106">
@@ -4616,36 +4592,36 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>B10BR</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="F106" t="n">
-        <v>0.01873325133359</v>
+        <v>0.0001608007619559388</v>
       </c>
       <c r="G106" t="n">
-        <v>0.01815902970821065</v>
+        <v>0.0003888368842493282</v>
       </c>
       <c r="H106" t="n">
-        <v>0.01269850865824583</v>
+        <v>1e-10</v>
       </c>
       <c r="I106" t="n">
-        <v>0.002012072434607646</v>
+        <v>1e-10</v>
       </c>
       <c r="J106" t="n">
-        <v>0.04134812873811623</v>
+        <v>0.001748251748251748</v>
       </c>
     </row>
     <row r="107">
@@ -4656,36 +4632,36 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>C57BL6</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="F107" t="n">
-        <v>0.07242901958775724</v>
+        <v>0.0004981482768320325</v>
       </c>
       <c r="G107" t="n">
-        <v>0.1216934767535491</v>
+        <v>0.001850667606973988</v>
       </c>
       <c r="H107" t="n">
-        <v>0.02762087044684924</v>
+        <v>3.142223311526303e-05</v>
       </c>
       <c r="I107" t="n">
-        <v>0.002699055330634278</v>
+        <v>1e-10</v>
       </c>
       <c r="J107" t="n">
-        <v>0.3177961069057589</v>
+        <v>0.01373626373626374</v>
       </c>
     </row>
     <row r="108">
@@ -4696,36 +4672,36 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>GYF</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F108" t="n">
-        <v>0.1177067489647653</v>
+        <v>0.0007295757529845903</v>
       </c>
       <c r="G108" t="n">
-        <v>0.1986969152852034</v>
+        <v>0.0009159181551378159</v>
       </c>
       <c r="H108" t="n">
-        <v>0.04236875725900116</v>
+        <v>0.0002660406885758999</v>
       </c>
       <c r="I108" t="n">
-        <v>0.002251004204466345</v>
+        <v>2.106361671058048e-05</v>
       </c>
       <c r="J108" t="n">
-        <v>0.7838364167478091</v>
+        <v>0.00209036674685734</v>
       </c>
     </row>
     <row r="109">
@@ -4736,36 +4712,36 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>HFL</t>
         </is>
       </c>
       <c r="E109" t="n">
         <v>6</v>
       </c>
       <c r="F109" t="n">
-        <v>0.002206263735744019</v>
+        <v>0.0001646194857665153</v>
       </c>
       <c r="G109" t="n">
-        <v>0.002799790483118688</v>
+        <v>0.0002526463930603215</v>
       </c>
       <c r="H109" t="n">
-        <v>0.001339833875045143</v>
+        <v>1.914549458536297e-05</v>
       </c>
       <c r="I109" t="n">
-        <v>0.00010990619808392</v>
+        <v>1e-10</v>
       </c>
       <c r="J109" t="n">
-        <v>0.007447192936082791</v>
+        <v>0.0005973715651135006</v>
       </c>
     </row>
     <row r="110">
@@ -4776,36 +4752,36 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0006358154308081924</v>
+        <v>0.0009376235312714902</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0006588645032822923</v>
+        <v>0.002894938962258286</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0004333618544944671</v>
+        <v>2.359485413862638e-05</v>
       </c>
       <c r="I110" t="n">
         <v>1e-10</v>
       </c>
       <c r="J110" t="n">
-        <v>0.001654259718775848</v>
+        <v>0.01373626373626374</v>
       </c>
     </row>
     <row r="111">
@@ -4816,36 +4792,36 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>GYF</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F111" t="n">
-        <v>0.009983094096589722</v>
+        <v>0.01378739586109934</v>
       </c>
       <c r="G111" t="n">
-        <v>0.02268585527548247</v>
+        <v>0.01409274180296961</v>
       </c>
       <c r="H111" t="n">
-        <v>0.001438198110649631</v>
+        <v>0.009044002761324164</v>
       </c>
       <c r="I111" t="n">
-        <v>1e-10</v>
+        <v>0.0008048289738430583</v>
       </c>
       <c r="J111" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.03666062547748293</v>
       </c>
     </row>
     <row r="112">
@@ -4856,36 +4832,36 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>B10BR</t>
+          <t>HFL</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0008885225506659297</v>
+        <v>0.0653784493116835</v>
       </c>
       <c r="G112" t="n">
-        <v>0.003057935996836243</v>
+        <v>0.1117229507973507</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0002406016065531423</v>
+        <v>0.02480726872743406</v>
       </c>
       <c r="I112" t="n">
-        <v>1e-10</v>
+        <v>0.002699055330634278</v>
       </c>
       <c r="J112" t="n">
-        <v>0.02465483234714004</v>
+        <v>0.2912121375763823</v>
       </c>
     </row>
     <row r="113">
@@ -4896,36 +4872,36 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CDR3a</t>
+          <t>CDR3</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>C57BL6</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="F113" t="n">
-        <v>0.003827417221277741</v>
+        <v>0.09569225485783588</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01183024932797594</v>
+        <v>0.1712020415227733</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0005860944663521397</v>
+        <v>0.0346335656213705</v>
       </c>
       <c r="I113" t="n">
-        <v>1e-10</v>
+        <v>0.001819723721307796</v>
       </c>
       <c r="J113" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.6783511846802986</v>
       </c>
     </row>
     <row r="114">
@@ -4936,34 +4912,36 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>B10BR SLO</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>351</v>
       </c>
       <c r="F114" t="n">
-        <v>1.701669145658016e-05</v>
-      </c>
-      <c r="G114" t="inlineStr"/>
+        <v>0.001357784249957524</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.006784993900018669</v>
+      </c>
       <c r="H114" t="n">
-        <v>1.701669145658016e-05</v>
+        <v>0.0001018507740658829</v>
       </c>
       <c r="I114" t="n">
-        <v>1.701669145658016e-05</v>
+        <v>1e-10</v>
       </c>
       <c r="J114" t="n">
-        <v>1.701669145658016e-05</v>
+        <v>0.1025641025641026</v>
       </c>
     </row>
     <row r="115">
@@ -4974,34 +4952,34 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>C57BL6 SLO</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="E115" t="n">
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>1.467332858777236e-05</v>
+        <v>7.68672735770055e-05</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>1.467332858777236e-05</v>
+        <v>7.68672735770055e-05</v>
       </c>
       <c r="I115" t="n">
-        <v>1.467332858777236e-05</v>
+        <v>7.68672735770055e-05</v>
       </c>
       <c r="J115" t="n">
-        <v>1.467332858777236e-05</v>
+        <v>7.68672735770055e-05</v>
       </c>
     </row>
     <row r="116">
@@ -5012,36 +4990,34 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>351</v>
+        <v>1</v>
       </c>
       <c r="F116" t="n">
-        <v>0.00156318209524434</v>
-      </c>
-      <c r="G116" t="n">
-        <v>0.006004885923264748</v>
-      </c>
+        <v>0.0001720323163889472</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>0.0001166393293238564</v>
+        <v>0.0001720323163889472</v>
       </c>
       <c r="I116" t="n">
-        <v>1e-10</v>
+        <v>0.0001720323163889472</v>
       </c>
       <c r="J116" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.0001720323163889472</v>
       </c>
     </row>
     <row r="117">
@@ -5052,36 +5028,34 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>B10BR SLO × C57BL6 SLO</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0006819178293232456</v>
-      </c>
-      <c r="G117" t="n">
-        <v>0.001503025368410236</v>
-      </c>
+        <v>8.978999592653821e-05</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>0.0001709401709401709</v>
+        <v>8.978999592653821e-05</v>
       </c>
       <c r="I117" t="n">
-        <v>1e-10</v>
+        <v>8.978999592653821e-05</v>
       </c>
       <c r="J117" t="n">
-        <v>0.005866243295602451</v>
+        <v>8.978999592653821e-05</v>
       </c>
     </row>
     <row r="118">
@@ -5092,36 +5066,34 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>C57BL6 SLO</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0004735873163531046</v>
-      </c>
-      <c r="G118" t="n">
-        <v>0.0005693307558712308</v>
-      </c>
+        <v>8.775872385622115e-05</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>0.0002648893113267449</v>
+        <v>8.775872385622115e-05</v>
       </c>
       <c r="I118" t="n">
-        <v>1.404547926184987e-05</v>
+        <v>8.775872385622115e-05</v>
       </c>
       <c r="J118" t="n">
-        <v>0.001792114695340502</v>
+        <v>8.775872385622115e-05</v>
       </c>
     </row>
     <row r="119">
@@ -5132,36 +5104,36 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>GYF</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="F119" t="n">
-        <v>0.00413839432406681</v>
+        <v>0.0009386401959776724</v>
       </c>
       <c r="G119" t="n">
-        <v>0.01032114186948946</v>
+        <v>0.001987478386181893</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0003167754444414102</v>
+        <v>0.0001358634119831529</v>
       </c>
       <c r="I119" t="n">
         <v>1e-10</v>
       </c>
       <c r="J119" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.007447192936082791</v>
       </c>
     </row>
     <row r="120">
@@ -5172,36 +5144,36 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>HFL</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F120" t="n">
-        <v>0.01830293056415361</v>
+        <v>0.0002915015961118109</v>
       </c>
       <c r="G120" t="n">
-        <v>0.01841813831561883</v>
+        <v>0.0004936605498207121</v>
       </c>
       <c r="H120" t="n">
-        <v>0.01249398426806507</v>
+        <v>8.549906820507024e-05</v>
       </c>
       <c r="I120" t="n">
-        <v>0.0008048289738430583</v>
+        <v>1e-10</v>
       </c>
       <c r="J120" t="n">
-        <v>0.04611802715041417</v>
+        <v>0.001654259718775848</v>
       </c>
     </row>
     <row r="121">
@@ -5212,36 +5184,36 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="F121" t="n">
-        <v>0.07203826284162722</v>
+        <v>0.002929806070046308</v>
       </c>
       <c r="G121" t="n">
-        <v>0.121418083652622</v>
+        <v>0.01158820516102467</v>
       </c>
       <c r="H121" t="n">
-        <v>0.02669367846374238</v>
+        <v>0.0002349394052117391</v>
       </c>
       <c r="I121" t="n">
-        <v>0.004048582995951417</v>
+        <v>1e-10</v>
       </c>
       <c r="J121" t="n">
-        <v>0.3174463121950434</v>
+        <v>0.1025641025641026</v>
       </c>
     </row>
     <row r="122">
@@ -5252,36 +5224,36 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>B10BR</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="F122" t="n">
-        <v>0.1207251175552363</v>
+        <v>0.0008885225506659297</v>
       </c>
       <c r="G122" t="n">
-        <v>0.1798045491683578</v>
+        <v>0.003057935996836243</v>
       </c>
       <c r="H122" t="n">
-        <v>0.04912950058072009</v>
+        <v>0.0002406016065531423</v>
       </c>
       <c r="I122" t="n">
-        <v>0.002392906887476745</v>
+        <v>1e-10</v>
       </c>
       <c r="J122" t="n">
-        <v>0.6994482310938007</v>
+        <v>0.02465483234714004</v>
       </c>
     </row>
     <row r="123">
@@ -5292,36 +5264,36 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>C57BL6</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="F123" t="n">
-        <v>0.001475078536629758</v>
+        <v>0.003827417221277741</v>
       </c>
       <c r="G123" t="n">
-        <v>0.002222573773506424</v>
+        <v>0.01183024932797594</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0004371729850940279</v>
+        <v>0.0005860944663521397</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0001709401709401709</v>
+        <v>1e-10</v>
       </c>
       <c r="J123" t="n">
-        <v>0.005866243295602451</v>
+        <v>0.1025641025641026</v>
       </c>
     </row>
     <row r="124">
@@ -5332,36 +5304,36 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>GYF</t>
         </is>
       </c>
       <c r="E124" t="n">
         <v>6</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0008875956794729296</v>
+        <v>0.002206263735744019</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0007234781577193988</v>
+        <v>0.002799790483118688</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0008125975979961076</v>
+        <v>0.001339833875045143</v>
       </c>
       <c r="I124" t="n">
-        <v>7.530968347609874e-05</v>
+        <v>0.00010990619808392</v>
       </c>
       <c r="J124" t="n">
-        <v>0.001792114695340502</v>
+        <v>0.007447192936082791</v>
       </c>
     </row>
     <row r="125">
@@ -5372,36 +5344,36 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>HFL</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0065734267501531</v>
+        <v>0.0006358154308081924</v>
       </c>
       <c r="G125" t="n">
-        <v>0.01744592197712574</v>
+        <v>0.0006588645032822923</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0003672589470422005</v>
+        <v>0.0004333618544944671</v>
       </c>
       <c r="I125" t="n">
         <v>1e-10</v>
       </c>
       <c r="J125" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.001654259718775848</v>
       </c>
     </row>
     <row r="126">
@@ -5412,36 +5384,36 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>B10BR</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="F126" t="n">
-        <v>0.002913788566514799</v>
+        <v>0.009983094096589722</v>
       </c>
       <c r="G126" t="n">
-        <v>0.009460211715598001</v>
+        <v>0.02268585527548247</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0001289617895205159</v>
+        <v>0.001438198110649631</v>
       </c>
       <c r="I126" t="n">
         <v>1e-10</v>
       </c>
       <c r="J126" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.1025641025641026</v>
       </c>
     </row>
     <row r="127">
@@ -5452,36 +5424,36 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CDR3b</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>C57BL6</t>
+          <t>GYF</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="F127" t="n">
-        <v>0.001970456538947975</v>
+        <v>0.01873325133359</v>
       </c>
       <c r="G127" t="n">
-        <v>0.006787103068719874</v>
+        <v>0.01815902970821065</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0002616615333156802</v>
+        <v>0.01269850865824583</v>
       </c>
       <c r="I127" t="n">
-        <v>1e-10</v>
+        <v>0.002012072434607646</v>
       </c>
       <c r="J127" t="n">
-        <v>0.05505354246627782</v>
+        <v>0.04134812873811623</v>
       </c>
     </row>
     <row r="128">
@@ -5492,34 +5464,36 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B10BR SLO</t>
+          <t>HFL</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F128" t="n">
-        <v>3.359567535096329e-05</v>
-      </c>
-      <c r="G128" t="inlineStr"/>
+        <v>0.07242901958775724</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.1216934767535491</v>
+      </c>
       <c r="H128" t="n">
-        <v>3.359567535096329e-05</v>
+        <v>0.02762087044684924</v>
       </c>
       <c r="I128" t="n">
-        <v>3.359567535096329e-05</v>
+        <v>0.002699055330634278</v>
       </c>
       <c r="J128" t="n">
-        <v>3.359567535096329e-05</v>
+        <v>0.3177961069057589</v>
       </c>
     </row>
     <row r="129">
@@ -5530,34 +5504,36 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3a</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>C57BL6 SLO</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F129" t="n">
-        <v>2.074796723341422e-05</v>
-      </c>
-      <c r="G129" t="inlineStr"/>
+        <v>0.1177067489647653</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.1986969152852034</v>
+      </c>
       <c r="H129" t="n">
-        <v>2.074796723341422e-05</v>
+        <v>0.04236875725900116</v>
       </c>
       <c r="I129" t="n">
-        <v>2.074796723341422e-05</v>
+        <v>0.002251004204466345</v>
       </c>
       <c r="J129" t="n">
-        <v>2.074796723341422e-05</v>
+        <v>0.7838364167478091</v>
       </c>
     </row>
     <row r="130">
@@ -5568,12 +5544,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5585,19 +5561,19 @@
         <v>351</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0006132730888222901</v>
+        <v>0.00156318209524434</v>
       </c>
       <c r="G130" t="n">
-        <v>0.004669820961287701</v>
+        <v>0.006004885923264748</v>
       </c>
       <c r="H130" t="n">
-        <v>1e-10</v>
+        <v>0.0001166393293238564</v>
       </c>
       <c r="I130" t="n">
         <v>1e-10</v>
       </c>
       <c r="J130" t="n">
-        <v>0.07869142351900972</v>
+        <v>0.06818181818181818</v>
       </c>
     </row>
     <row r="131">
@@ -5608,36 +5584,34 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0007107329337501481</v>
-      </c>
-      <c r="G131" t="n">
-        <v>0.001731023111951273</v>
-      </c>
+        <v>3.547367311941806e-05</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>1e-10</v>
+        <v>3.547367311941806e-05</v>
       </c>
       <c r="I131" t="n">
-        <v>1e-10</v>
+        <v>3.547367311941806e-05</v>
       </c>
       <c r="J131" t="n">
-        <v>0.006585617206085569</v>
+        <v>3.547367311941806e-05</v>
       </c>
     </row>
     <row r="132">
@@ -5648,36 +5622,34 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0001813538622679531</v>
-      </c>
-      <c r="G132" t="n">
-        <v>0.0004380732483695505</v>
-      </c>
+        <v>1.701669145658016e-05</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>1e-10</v>
+        <v>1.701669145658016e-05</v>
       </c>
       <c r="I132" t="n">
-        <v>1e-10</v>
+        <v>1.701669145658016e-05</v>
       </c>
       <c r="J132" t="n">
-        <v>0.001654259718775848</v>
+        <v>1.701669145658016e-05</v>
       </c>
     </row>
     <row r="133">
@@ -5688,36 +5660,34 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>B10BR SLO × C57BL6 SLO</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>0.00119275371239902</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0.007911281178785258</v>
-      </c>
+        <v>1.044117906365516e-05</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>1e-10</v>
+        <v>1.044117906365516e-05</v>
       </c>
       <c r="I133" t="n">
-        <v>1e-10</v>
+        <v>1.044117906365516e-05</v>
       </c>
       <c r="J133" t="n">
-        <v>0.07869142351900972</v>
+        <v>1.044117906365516e-05</v>
       </c>
     </row>
     <row r="134">
@@ -5728,36 +5698,34 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>C57BL6 SLO</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F134" t="n">
-        <v>0.01744451826846779</v>
-      </c>
-      <c r="G134" t="n">
-        <v>0.01747433436661695</v>
-      </c>
+        <v>1.467332858777236e-05</v>
+      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>0.01027528297205356</v>
+        <v>1.467332858777236e-05</v>
       </c>
       <c r="I134" t="n">
-        <v>0.002012072434607646</v>
+        <v>1.467332858777236e-05</v>
       </c>
       <c r="J134" t="n">
-        <v>0.03935650867508528</v>
+        <v>1.467332858777236e-05</v>
       </c>
     </row>
     <row r="135">
@@ -5768,36 +5736,36 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>GYF</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F135" t="n">
-        <v>0.07142657893881711</v>
+        <v>0.0006819178293232456</v>
       </c>
       <c r="G135" t="n">
-        <v>0.1209568733332108</v>
+        <v>0.001503025368410236</v>
       </c>
       <c r="H135" t="n">
-        <v>0.02642042788738032</v>
+        <v>0.0001709401709401709</v>
       </c>
       <c r="I135" t="n">
-        <v>0.002699055330634278</v>
+        <v>1e-10</v>
       </c>
       <c r="J135" t="n">
-        <v>0.3154219881427934</v>
+        <v>0.005866243295602451</v>
       </c>
     </row>
     <row r="136">
@@ -5808,36 +5776,36 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>HFL</t>
         </is>
       </c>
       <c r="E136" t="n">
         <v>15</v>
       </c>
       <c r="F136" t="n">
-        <v>0.1141523492731125</v>
+        <v>0.0004735873163531046</v>
       </c>
       <c r="G136" t="n">
-        <v>0.1987283490520821</v>
+        <v>0.0005693307558712308</v>
       </c>
       <c r="H136" t="n">
-        <v>0.04112311265969803</v>
+        <v>0.0002648893113267449</v>
       </c>
       <c r="I136" t="n">
-        <v>0.002023959911649705</v>
+        <v>1.404547926184987e-05</v>
       </c>
       <c r="J136" t="n">
-        <v>0.7838364167478091</v>
+        <v>0.001792114695340502</v>
       </c>
     </row>
     <row r="137">
@@ -5848,36 +5816,36 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="F137" t="n">
-        <v>0.001776832184375371</v>
+        <v>0.00413839432406681</v>
       </c>
       <c r="G137" t="n">
-        <v>0.002473236667838158</v>
+        <v>0.01032114186948946</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0008884073672806067</v>
+        <v>0.0003167754444414102</v>
       </c>
       <c r="I137" t="n">
-        <v>8.529722014482592e-05</v>
+        <v>1e-10</v>
       </c>
       <c r="J137" t="n">
-        <v>0.006585617206085569</v>
+        <v>0.06818181818181818</v>
       </c>
     </row>
     <row r="138">
@@ -5888,36 +5856,36 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>B10BR</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0004533845056698827</v>
+        <v>0.002913788566514799</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0006239723845847699</v>
+        <v>0.009460211715598001</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0002034902918496013</v>
+        <v>0.0001289617895205159</v>
       </c>
       <c r="I138" t="n">
         <v>1e-10</v>
       </c>
       <c r="J138" t="n">
-        <v>0.001654259718775848</v>
+        <v>0.06818181818181818</v>
       </c>
     </row>
     <row r="139">
@@ -5928,36 +5896,36 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>C57BL6</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="F139" t="n">
-        <v>0.004972107133601986</v>
+        <v>0.001970456538947975</v>
       </c>
       <c r="G139" t="n">
-        <v>0.01623351868778429</v>
+        <v>0.006787103068719874</v>
       </c>
       <c r="H139" t="n">
-        <v>0.0001526090710009458</v>
+        <v>0.0002616615333156802</v>
       </c>
       <c r="I139" t="n">
         <v>1e-10</v>
       </c>
       <c r="J139" t="n">
-        <v>0.07869142351900972</v>
+        <v>0.05505354246627782</v>
       </c>
     </row>
     <row r="140">
@@ -5968,36 +5936,36 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>B10BR</t>
+          <t>GYF</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0002522947927066079</v>
+        <v>0.001475078536629758</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0005222205163126044</v>
+        <v>0.002222573773506424</v>
       </c>
       <c r="H140" t="n">
-        <v>1e-10</v>
+        <v>0.0004371729850940279</v>
       </c>
       <c r="I140" t="n">
-        <v>1e-10</v>
+        <v>0.0001709401709401709</v>
       </c>
       <c r="J140" t="n">
-        <v>0.002065727699530516</v>
+        <v>0.005866243295602451</v>
       </c>
     </row>
     <row r="141">
@@ -6008,36 +5976,36 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>FullAlpha</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>C57BL6</t>
+          <t>HFL</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="F141" t="n">
-        <v>0.00187572583855634</v>
+        <v>0.0008875956794729296</v>
       </c>
       <c r="G141" t="n">
-        <v>0.008419683839266418</v>
+        <v>0.0007234781577193988</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0001368724205373087</v>
+        <v>0.0008125975979961076</v>
       </c>
       <c r="I141" t="n">
-        <v>1e-10</v>
+        <v>7.530968347609874e-05</v>
       </c>
       <c r="J141" t="n">
-        <v>0.07869142351900972</v>
+        <v>0.001792114695340502</v>
       </c>
     </row>
     <row r="142">
@@ -6048,34 +6016,36 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>B10BR SLO</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F142" t="n">
-        <v>9.542409372055383e-06</v>
-      </c>
-      <c r="G142" t="inlineStr"/>
+        <v>0.0065734267501531</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.01744592197712574</v>
+      </c>
       <c r="H142" t="n">
-        <v>9.542409372055383e-06</v>
+        <v>0.0003672589470422005</v>
       </c>
       <c r="I142" t="n">
-        <v>9.542409372055383e-06</v>
+        <v>1e-10</v>
       </c>
       <c r="J142" t="n">
-        <v>9.542409372055383e-06</v>
+        <v>0.06818181818181818</v>
       </c>
     </row>
     <row r="143">
@@ -6086,34 +6056,36 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>C57BL6 SLO</t>
+          <t>GYF</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F143" t="n">
-        <v>4.229840548900228e-06</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
+        <v>0.01830293056415361</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.01841813831561883</v>
+      </c>
       <c r="H143" t="n">
-        <v>4.229840548900228e-06</v>
+        <v>0.01249398426806507</v>
       </c>
       <c r="I143" t="n">
-        <v>4.229840548900228e-06</v>
+        <v>0.0008048289738430583</v>
       </c>
       <c r="J143" t="n">
-        <v>4.229840548900228e-06</v>
+        <v>0.04611802715041417</v>
       </c>
     </row>
     <row r="144">
@@ -6124,36 +6096,36 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>HFL</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>351</v>
+        <v>6</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0006672593507086774</v>
+        <v>0.07203826284162722</v>
       </c>
       <c r="G144" t="n">
-        <v>0.004079177228659587</v>
+        <v>0.121418083652622</v>
       </c>
       <c r="H144" t="n">
-        <v>1e-10</v>
+        <v>0.02669367846374238</v>
       </c>
       <c r="I144" t="n">
-        <v>1e-10</v>
+        <v>0.004048582995951417</v>
       </c>
       <c r="J144" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.3174463121950434</v>
       </c>
     </row>
     <row r="145">
@@ -6164,36 +6136,36 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>CDR3b</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="E145" t="n">
         <v>15</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0005846332388229272</v>
+        <v>0.1207251175552363</v>
       </c>
       <c r="G145" t="n">
-        <v>0.00150859366225173</v>
+        <v>0.1798045491683578</v>
       </c>
       <c r="H145" t="n">
-        <v>1e-10</v>
+        <v>0.04912950058072009</v>
       </c>
       <c r="I145" t="n">
-        <v>1e-10</v>
+        <v>0.002392906887476745</v>
       </c>
       <c r="J145" t="n">
-        <v>0.005801834236175474</v>
+        <v>0.6994482310938007</v>
       </c>
     </row>
     <row r="146">
@@ -6204,27 +6176,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>15</v>
+        <v>351</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0002646067452343278</v>
+        <v>0.0006132730888222901</v>
       </c>
       <c r="G146" t="n">
-        <v>0.000501578880896486</v>
+        <v>0.004669820961287701</v>
       </c>
       <c r="H146" t="n">
         <v>1e-10</v>
@@ -6233,7 +6205,7 @@
         <v>1e-10</v>
       </c>
       <c r="J146" t="n">
-        <v>0.001792114695340502</v>
+        <v>0.07869142351900972</v>
       </c>
     </row>
     <row r="147">
@@ -6244,36 +6216,34 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="F147" t="n">
-        <v>0.001545263980266946</v>
-      </c>
-      <c r="G147" t="n">
-        <v>0.007167011087992708</v>
-      </c>
+        <v>1.83563638392849e-07</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>1e-10</v>
+        <v>1.83563638392849e-07</v>
       </c>
       <c r="I147" t="n">
-        <v>1e-10</v>
+        <v>1.83563638392849e-07</v>
       </c>
       <c r="J147" t="n">
-        <v>0.06818181818181818</v>
+        <v>1.83563638392849e-07</v>
       </c>
     </row>
     <row r="148">
@@ -6284,36 +6254,34 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F148" t="n">
-        <v>0.01825061588086396</v>
-      </c>
-      <c r="G148" t="n">
-        <v>0.01837529630922191</v>
-      </c>
+        <v>3.359567535096329e-05</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
-        <v>0.01242408352711722</v>
+        <v>3.359567535096329e-05</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0008048289738430583</v>
+        <v>3.359567535096329e-05</v>
       </c>
       <c r="J148" t="n">
-        <v>0.04603169399517733</v>
+        <v>3.359567535096329e-05</v>
       </c>
     </row>
     <row r="149">
@@ -6324,36 +6292,34 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>B10BR SLO × C57BL6 SLO</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0707023386035134</v>
-      </c>
-      <c r="G149" t="n">
-        <v>0.1193737107616653</v>
-      </c>
+        <v>1.35988030037174e-05</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
-        <v>0.02665003718277858</v>
+        <v>1.35988030037174e-05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.002699055330634278</v>
+        <v>1.35988030037174e-05</v>
       </c>
       <c r="J149" t="n">
-        <v>0.3119050196698437</v>
+        <v>1.35988030037174e-05</v>
       </c>
     </row>
     <row r="150">
@@ -6364,36 +6330,34 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>C57BL6 SLO</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F150" t="n">
-        <v>0.1206402025239933</v>
-      </c>
-      <c r="G150" t="n">
-        <v>0.1798477052462389</v>
-      </c>
+        <v>2.074796723341422e-05</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>0.04909088269454123</v>
+        <v>2.074796723341422e-05</v>
       </c>
       <c r="I150" t="n">
-        <v>0.002351826384723962</v>
+        <v>2.074796723341422e-05</v>
       </c>
       <c r="J150" t="n">
-        <v>0.6994482310938007</v>
+        <v>2.074796723341422e-05</v>
       </c>
     </row>
     <row r="151">
@@ -6404,12 +6368,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6418,22 +6382,22 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F151" t="n">
-        <v>0.001461582947057318</v>
+        <v>0.0007107329337501481</v>
       </c>
       <c r="G151" t="n">
-        <v>0.002198706884570174</v>
+        <v>0.001731023111951273</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0004317061800069566</v>
+        <v>1e-10</v>
       </c>
       <c r="I151" t="n">
-        <v>0.0001709401709401709</v>
+        <v>1e-10</v>
       </c>
       <c r="J151" t="n">
-        <v>0.005801834236175474</v>
+        <v>0.006585617206085569</v>
       </c>
     </row>
     <row r="152">
@@ -6444,12 +6408,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6458,22 +6422,22 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0006615167130858196</v>
+        <v>0.0001813538622679531</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0006239814110789641</v>
+        <v>0.0004380732483695505</v>
       </c>
       <c r="H152" t="n">
-        <v>0.0005608903234266378</v>
+        <v>1e-10</v>
       </c>
       <c r="I152" t="n">
-        <v>5.678889812611355e-05</v>
+        <v>1e-10</v>
       </c>
       <c r="J152" t="n">
-        <v>0.001792114695340502</v>
+        <v>0.001654259718775848</v>
       </c>
     </row>
     <row r="153">
@@ -6484,12 +6448,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6498,22 +6462,22 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="F153" t="n">
-        <v>0.004197648683610351</v>
+        <v>0.00119275371239902</v>
       </c>
       <c r="G153" t="n">
-        <v>0.01411356377273175</v>
+        <v>0.007911281178785258</v>
       </c>
       <c r="H153" t="n">
-        <v>7.086736649094887e-05</v>
+        <v>1e-10</v>
       </c>
       <c r="I153" t="n">
         <v>1e-10</v>
       </c>
       <c r="J153" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.07869142351900972</v>
       </c>
     </row>
     <row r="154">
@@ -6524,12 +6488,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6541,10 +6505,10 @@
         <v>66</v>
       </c>
       <c r="F154" t="n">
-        <v>0.001489590561339832</v>
+        <v>0.0002522947927066079</v>
       </c>
       <c r="G154" t="n">
-        <v>0.008416703420893446</v>
+        <v>0.0005222205163126044</v>
       </c>
       <c r="H154" t="n">
         <v>1e-10</v>
@@ -6553,7 +6517,7 @@
         <v>1e-10</v>
       </c>
       <c r="J154" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.002065727699530516</v>
       </c>
     </row>
     <row r="155">
@@ -6564,12 +6528,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>FullBeta</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6581,19 +6545,19 @@
         <v>105</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0007271833896643908</v>
+        <v>0.00187572583855634</v>
       </c>
       <c r="G155" t="n">
-        <v>0.002377425261538886</v>
+        <v>0.008419683839266418</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0001086748339176088</v>
+        <v>0.0001368724205373087</v>
       </c>
       <c r="I155" t="n">
         <v>1e-10</v>
       </c>
       <c r="J155" t="n">
-        <v>0.01774267399267399</v>
+        <v>0.07869142351900972</v>
       </c>
     </row>
     <row r="156">
@@ -6604,34 +6568,36 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>B10BR SLO</t>
+          <t>GYF</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F156" t="n">
-        <v>1.8798567824958e-08</v>
-      </c>
-      <c r="G156" t="inlineStr"/>
+        <v>0.001776832184375371</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.002473236667838158</v>
+      </c>
       <c r="H156" t="n">
-        <v>1.8798567824958e-08</v>
+        <v>0.0008884073672806067</v>
       </c>
       <c r="I156" t="n">
-        <v>1.8798567824958e-08</v>
+        <v>8.529722014482592e-05</v>
       </c>
       <c r="J156" t="n">
-        <v>1.8798567824958e-08</v>
+        <v>0.006585617206085569</v>
       </c>
     </row>
     <row r="157">
@@ -6642,34 +6608,36 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>C57BL6 SLO</t>
+          <t>HFL</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F157" t="n">
-        <v>3.361573602129544e-08</v>
-      </c>
-      <c r="G157" t="inlineStr"/>
+        <v>0.0004533845056698827</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.0006239723845847699</v>
+      </c>
       <c r="H157" t="n">
-        <v>3.361573602129544e-08</v>
+        <v>0.0002034902918496013</v>
       </c>
       <c r="I157" t="n">
-        <v>3.361573602129544e-08</v>
+        <v>1e-10</v>
       </c>
       <c r="J157" t="n">
-        <v>3.361573602129544e-08</v>
+        <v>0.001654259718775848</v>
       </c>
     </row>
     <row r="158">
@@ -6680,36 +6648,36 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>351</v>
+        <v>24</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0001223230370342846</v>
+        <v>0.004972107133601986</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0008839366484923771</v>
+        <v>0.01623351868778429</v>
       </c>
       <c r="H158" t="n">
-        <v>1e-10</v>
+        <v>0.0001526090710009458</v>
       </c>
       <c r="I158" t="n">
         <v>1e-10</v>
       </c>
       <c r="J158" t="n">
-        <v>0.01316391941391941</v>
+        <v>0.07869142351900972</v>
       </c>
     </row>
     <row r="159">
@@ -6720,12 +6688,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -6734,22 +6702,22 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F159" t="n">
-        <v>0.000262027803149796</v>
+        <v>0.01744451826846779</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0006490796332874673</v>
+        <v>0.01747433436661695</v>
       </c>
       <c r="H159" t="n">
-        <v>1e-10</v>
+        <v>0.01027528297205356</v>
       </c>
       <c r="I159" t="n">
-        <v>1e-10</v>
+        <v>0.002012072434607646</v>
       </c>
       <c r="J159" t="n">
-        <v>0.002010064542896434</v>
+        <v>0.03935650867508528</v>
       </c>
     </row>
     <row r="160">
@@ -6760,12 +6728,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -6774,22 +6742,22 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F160" t="n">
-        <v>9.716814164090766e-06</v>
+        <v>0.07142657893881711</v>
       </c>
       <c r="G160" t="n">
-        <v>2.926066774436934e-05</v>
+        <v>0.1209568733332108</v>
       </c>
       <c r="H160" t="n">
-        <v>1e-10</v>
+        <v>0.02642042788738032</v>
       </c>
       <c r="I160" t="n">
-        <v>1e-10</v>
+        <v>0.002699055330634278</v>
       </c>
       <c r="J160" t="n">
-        <v>0.000112051646723871</v>
+        <v>0.3154219881427934</v>
       </c>
     </row>
     <row r="161">
@@ -6800,12 +6768,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullAlpha</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -6814,22 +6782,22 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0002112219088001026</v>
+        <v>0.1141523492731125</v>
       </c>
       <c r="G161" t="n">
-        <v>0.001309629263361664</v>
+        <v>0.1987283490520821</v>
       </c>
       <c r="H161" t="n">
-        <v>1e-10</v>
+        <v>0.04112311265969803</v>
       </c>
       <c r="I161" t="n">
-        <v>1e-10</v>
+        <v>0.002023959911649705</v>
       </c>
       <c r="J161" t="n">
-        <v>0.01316391941391941</v>
+        <v>0.7838364167478091</v>
       </c>
     </row>
     <row r="162">
@@ -6840,36 +6808,36 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6</v>
+        <v>351</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0132924043330923</v>
+        <v>0.0006672593507086774</v>
       </c>
       <c r="G162" t="n">
-        <v>0.01378842037119685</v>
+        <v>0.004079177228659587</v>
       </c>
       <c r="H162" t="n">
-        <v>0.008130115296339259</v>
+        <v>1e-10</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0008048289738430583</v>
+        <v>1e-10</v>
       </c>
       <c r="J162" t="n">
-        <v>0.03568908297225431</v>
+        <v>0.06818181818181818</v>
       </c>
     </row>
     <row r="163">
@@ -6880,36 +6848,34 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F163" t="n">
-        <v>0.06491605844543795</v>
-      </c>
-      <c r="G163" t="n">
-        <v>0.1114547575746722</v>
-      </c>
+        <v>1.376727287946367e-07</v>
+      </c>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>0.02431553598418002</v>
+        <v>1.376727287946367e-07</v>
       </c>
       <c r="I163" t="n">
-        <v>0.002699055330634278</v>
+        <v>1.376727287946367e-07</v>
       </c>
       <c r="J163" t="n">
-        <v>0.2902769796241488</v>
+        <v>1.376727287946367e-07</v>
       </c>
     </row>
     <row r="164">
@@ -6920,36 +6886,34 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F164" t="n">
-        <v>0.09496163749346424</v>
-      </c>
-      <c r="G164" t="n">
-        <v>0.1713332084655425</v>
-      </c>
+        <v>9.542409372055383e-06</v>
+      </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>0.03448577235772358</v>
+        <v>9.542409372055383e-06</v>
       </c>
       <c r="I164" t="n">
-        <v>0.001781364639873021</v>
+        <v>9.542409372055383e-06</v>
       </c>
       <c r="J164" t="n">
-        <v>0.6783511846802986</v>
+        <v>9.542409372055383e-06</v>
       </c>
     </row>
     <row r="165">
@@ -6960,36 +6924,34 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>GYF</t>
+          <t>B10BR SLO × C57BL6 SLO</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F165" t="n">
-        <v>0.00065506935787449</v>
-      </c>
-      <c r="G165" t="n">
-        <v>0.0009331071264840125</v>
-      </c>
+        <v>2.486827862711209e-06</v>
+      </c>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
-        <v>0.0001056162745872558</v>
+        <v>2.486827862711209e-06</v>
       </c>
       <c r="I165" t="n">
-        <v>1e-10</v>
+        <v>2.486827862711209e-06</v>
       </c>
       <c r="J165" t="n">
-        <v>0.002010064542896434</v>
+        <v>2.486827862711209e-06</v>
       </c>
     </row>
     <row r="166">
@@ -7000,36 +6962,34 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>HFL</t>
+          <t>C57BL6 SLO</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F166" t="n">
-        <v>2.429188541022691e-05</v>
-      </c>
-      <c r="G166" t="n">
-        <v>4.441235516734016e-05</v>
-      </c>
+        <v>4.229840548900228e-06</v>
+      </c>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="n">
-        <v>2.514461256123818e-06</v>
+        <v>4.229840548900228e-06</v>
       </c>
       <c r="I166" t="n">
-        <v>1e-10</v>
+        <v>4.229840548900228e-06</v>
       </c>
       <c r="J166" t="n">
-        <v>0.000112051646723871</v>
+        <v>4.229840548900228e-06</v>
       </c>
     </row>
     <row r="167">
@@ -7040,36 +7000,36 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>GYF</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0007199912139491496</v>
+        <v>0.0005846332388229272</v>
       </c>
       <c r="G167" t="n">
-        <v>0.00268952024789428</v>
+        <v>0.00150859366225173</v>
       </c>
       <c r="H167" t="n">
-        <v>8.551598018112292e-08</v>
+        <v>1e-10</v>
       </c>
       <c r="I167" t="n">
         <v>1e-10</v>
       </c>
       <c r="J167" t="n">
-        <v>0.01316391941391941</v>
+        <v>0.005801834236175474</v>
       </c>
     </row>
     <row r="168">
@@ -7080,27 +7040,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>B10BR</t>
+          <t>HFL</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="F168" t="n">
-        <v>0.0001285736718507947</v>
+        <v>0.0002646067452343278</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0003778472440203651</v>
+        <v>0.000501578880896486</v>
       </c>
       <c r="H168" t="n">
         <v>1e-10</v>
@@ -7109,7 +7069,7 @@
         <v>1e-10</v>
       </c>
       <c r="J168" t="n">
-        <v>0.001748251748251748</v>
+        <v>0.001792114695340502</v>
       </c>
     </row>
     <row r="169">
@@ -7120,36 +7080,988 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FullChain</t>
+          <t>FullBeta</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>C57BL6</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="E169" t="n">
         <v>105</v>
       </c>
       <c r="F169" t="n">
+        <v>0.001545263980266946</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.007167011087992708</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I169" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Same strain, different epitope</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>B10BR</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>66</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.001489590561339832</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.008416703420893446</v>
+      </c>
+      <c r="H170" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I170" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Same strain, different epitope</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>C57BL6</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>105</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.0007271833896643908</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.002377425261538886</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.0001086748339176088</v>
+      </c>
+      <c r="I171" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0.01774267399267399</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Same strain, same epitope</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>6</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.001461582947057318</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.002198706884570174</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.0004317061800069566</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0.0001709401709401709</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0.005801834236175474</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Same strain, same epitope</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>6</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.0006615167130858196</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.0006239814110789641</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.0005608903234266378</v>
+      </c>
+      <c r="I173" t="n">
+        <v>5.678889812611355e-05</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0.001792114695340502</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Same strain, same epitope</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>24</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.004197648683610351</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.01411356377273175</v>
+      </c>
+      <c r="H174" t="n">
+        <v>7.086736649094887e-05</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Single mouse</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>6</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.01825061588086396</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.01837529630922191</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.01242408352711722</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0.0008048289738430583</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0.04603169399517733</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Single mouse</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>6</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.0707023386035134</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.1193737107616653</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.02665003718277858</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0.002699055330634278</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0.3119050196698437</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>FullBeta</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Single mouse</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>15</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.1206402025239933</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.1798477052462389</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.04909088269454123</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0.002351826384723962</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0.6994482310938007</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Cross-strain baseline</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>351</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.0001223230370342846</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0.0008839366484923771</v>
+      </c>
+      <c r="H178" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I178" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0.01316391941391941</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoire</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>B10BR Kb × B10BR Kd</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I179" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoire</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>B10BR SLO</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1.8798567824958e-08</v>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="n">
+        <v>1.8798567824958e-08</v>
+      </c>
+      <c r="I180" t="n">
+        <v>1.8798567824958e-08</v>
+      </c>
+      <c r="J180" t="n">
+        <v>1.8798567824958e-08</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoire</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>B10BR SLO × C57BL6 SLO</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1.845889040591741e-10</v>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="n">
+        <v>1.845889040591741e-10</v>
+      </c>
+      <c r="I181" t="n">
+        <v>1.845889040591741e-10</v>
+      </c>
+      <c r="J181" t="n">
+        <v>1.845889040591741e-10</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoire</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>C57BL6 SLO</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>3.361573602129544e-08</v>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="n">
+        <v>3.361573602129544e-08</v>
+      </c>
+      <c r="I182" t="n">
+        <v>3.361573602129544e-08</v>
+      </c>
+      <c r="J182" t="n">
+        <v>3.361573602129544e-08</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Same epitope, different strain</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>15</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.000262027803149796</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0.0006490796332874673</v>
+      </c>
+      <c r="H183" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I183" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0.002010064542896434</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Same epitope, different strain</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>15</v>
+      </c>
+      <c r="F184" t="n">
+        <v>9.716814164090766e-06</v>
+      </c>
+      <c r="G184" t="n">
+        <v>2.926066774436934e-05</v>
+      </c>
+      <c r="H184" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I184" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0.000112051646723871</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Same epitope, different strain</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>105</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.0002112219088001026</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.001309629263361664</v>
+      </c>
+      <c r="H185" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I185" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0.01316391941391941</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Same strain, different epitope</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>B10BR</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>66</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.0001285736718507947</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0.0003778472440203651</v>
+      </c>
+      <c r="H186" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="I186" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0.001748251748251748</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Same strain, different epitope</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>C57BL6</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>105</v>
+      </c>
+      <c r="F187" t="n">
         <v>0.0003280905300655374</v>
       </c>
-      <c r="G169" t="n">
+      <c r="G187" t="n">
         <v>0.001572139698737131</v>
       </c>
-      <c r="H169" t="n">
+      <c r="H187" t="n">
         <v>1.60296883767597e-05</v>
       </c>
-      <c r="I169" t="n">
-        <v>1e-10</v>
-      </c>
-      <c r="J169" t="n">
+      <c r="I187" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J187" t="n">
         <v>0.01316391941391941</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Same strain, same epitope</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>6</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.00065506935787449</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.0009331071264840125</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.0001056162745872558</v>
+      </c>
+      <c r="I188" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0.002010064542896434</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Same strain, same epitope</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>6</v>
+      </c>
+      <c r="F189" t="n">
+        <v>2.429188541022691e-05</v>
+      </c>
+      <c r="G189" t="n">
+        <v>4.441235516734016e-05</v>
+      </c>
+      <c r="H189" t="n">
+        <v>2.514461256123818e-06</v>
+      </c>
+      <c r="I189" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0.000112051646723871</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Same strain, same epitope</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>24</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.0007199912139491496</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.00268952024789428</v>
+      </c>
+      <c r="H190" t="n">
+        <v>8.551598018112292e-08</v>
+      </c>
+      <c r="I190" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0.01316391941391941</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Single mouse</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>GYF</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>6</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.0132924043330923</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.01378842037119685</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.008130115296339259</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0.0008048289738430583</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0.03568908297225431</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Single mouse</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>HFL</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>6</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0.06491605844543795</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.1114547575746722</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0.02431553598418002</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0.002699055330634278</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0.2902769796241488</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>FullChain</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Single mouse</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SYF</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>15</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.09496163749346424</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0.1713332084655425</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0.03448577235772358</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0.001781364639873021</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0.6783511846802986</v>
       </c>
     </row>
   </sheetData>

--- a/Final_Figures_and_Sheets_Singleset/pc_subset_statistics.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/pc_subset_statistics.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">

--- a/Final_Figures_and_Sheets_Singleset/pc_subset_statistics.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/pc_subset_statistics.xlsx
@@ -4766,16 +4766,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0009376235312714902</v>
+        <v>0.0007023437586346392</v>
       </c>
       <c r="G110" t="n">
-        <v>0.002894938962258286</v>
+        <v>0.002270856540591734</v>
       </c>
       <c r="H110" t="n">
-        <v>2.359485413862638e-05</v>
+        <v>3.417167851284855e-05</v>
       </c>
       <c r="I110" t="n">
         <v>1e-10</v>
@@ -5398,16 +5398,16 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="F126" t="n">
-        <v>0.009983094096589722</v>
+        <v>0.00586441549288639</v>
       </c>
       <c r="G126" t="n">
-        <v>0.02268585527548247</v>
+        <v>0.01619140864001013</v>
       </c>
       <c r="H126" t="n">
-        <v>0.001438198110649631</v>
+        <v>0.0008121813370499013</v>
       </c>
       <c r="I126" t="n">
         <v>1e-10</v>
@@ -6030,16 +6030,16 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0065734267501531</v>
+        <v>0.005864110052350202</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01744592197712574</v>
+        <v>0.01358509054079972</v>
       </c>
       <c r="H142" t="n">
-        <v>0.0003672589470422005</v>
+        <v>0.0004610280962762836</v>
       </c>
       <c r="I142" t="n">
         <v>1e-10</v>
@@ -6662,16 +6662,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="F158" t="n">
-        <v>0.004972107133601986</v>
+        <v>0.002427885645721225</v>
       </c>
       <c r="G158" t="n">
-        <v>0.01623351868778429</v>
+        <v>0.01127602153691039</v>
       </c>
       <c r="H158" t="n">
-        <v>0.0001526090710009458</v>
+        <v>1e-10</v>
       </c>
       <c r="I158" t="n">
         <v>1e-10</v>
@@ -7294,16 +7294,16 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="F174" t="n">
-        <v>0.004197648683610351</v>
+        <v>0.002053034514286041</v>
       </c>
       <c r="G174" t="n">
-        <v>0.01411356377273175</v>
+        <v>0.009790817951026697</v>
       </c>
       <c r="H174" t="n">
-        <v>7.086736649094887e-05</v>
+        <v>1e-10</v>
       </c>
       <c r="I174" t="n">
         <v>1e-10</v>
@@ -7926,16 +7926,16 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="F190" t="n">
-        <v>0.0007199912139491496</v>
+        <v>0.0004348685298825642</v>
       </c>
       <c r="G190" t="n">
-        <v>0.00268952024789428</v>
+        <v>0.001862328093394082</v>
       </c>
       <c r="H190" t="n">
-        <v>8.551598018112292e-08</v>
+        <v>9.885721064494444e-06</v>
       </c>
       <c r="I190" t="n">
         <v>1e-10</v>
